--- a/セリフ編集/キャラタイプ別/蠱惑×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×ノーマル.xlsx
@@ -328,7 +328,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H289"/>
+  <dimension ref="A1:H304"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3330,7 +3330,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.normal.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3340,12 +3340,12 @@
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.normal.seductive[1]</t>
+          <t xml:space="preserve">accepted.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3355,14 +3355,14 @@
       </c>
       <c r="F94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかったわ。もう少し続けてみる</t>
+          <t xml:space="preserve">…いろいろ、ありがとう。新しい場所でも闘い続けるわ</t>
         </is>
       </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.normal.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.normal.seductive[2]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.normal.seductive[1]</t>
+          <t xml:space="preserve">accepted.normal.seductive[2]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3387,14 +3387,14 @@
       </c>
       <c r="F95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう少しだけ…あのベルトに手を伸ばしたいの</t>
+          <t xml:space="preserve">ここで過ごした日々は、忘れないの</t>
         </is>
       </c>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.normal.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3404,12 +3404,12 @@
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.normal.seductive[1]</t>
+          <t xml:space="preserve">defended.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3419,14 +3419,14 @@
       </c>
       <c r="F96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ使い道があるのね。いいわ、付き合ってあげる</t>
+          <t xml:space="preserve">…ここに残れて、ほっとしたの</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.normal.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.normal.seductive[2]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.normal.seductive[1]</t>
+          <t xml:space="preserve">defended.normal.seductive[2]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3451,14 +3451,14 @@
       </c>
       <c r="F97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたがそう言うなら…もう少し頑張ってみるわ</t>
+          <t xml:space="preserve">社長…ありがとう。期待には応えるわ</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.normal.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.normal.seductive[1]</t>
+          <t xml:space="preserve">defense_failed.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3483,14 +3483,14 @@
       </c>
       <c r="F98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後にいい試合がしたいの。お願いできる？</t>
+          <t xml:space="preserve">…ごめんなさい。新しい場所で、答えを出すわ</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.normal.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.normal.seductive[2]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.normal.seductive[1]</t>
+          <t xml:space="preserve">defense_failed.normal.seductive[2]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3515,14 +3515,14 @@
       </c>
       <c r="F99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ…言われなくても辞めるつもりだったわ</t>
+          <t xml:space="preserve">お世話になりました。…また、どこかで</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.normal.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3532,12 +3532,12 @@
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.normal.seductive[1]</t>
+          <t xml:space="preserve">default.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3547,14 +3547,14 @@
       </c>
       <c r="F100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかったわ。潮時よね</t>
+          <t xml:space="preserve">…わかったわ。もう少し続けてみる</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.normal.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="C101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.normal.seductive[1]</t>
+          <t xml:space="preserve">former_champ.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3579,14 +3579,14 @@
       </c>
       <c r="F101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかったわ。もう限界なのよね</t>
+          <t xml:space="preserve">もう少しだけ…あのベルトに手を伸ばしたいの</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.normal.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.normal.seductive[1]</t>
+          <t xml:space="preserve">heel.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3611,14 +3611,14 @@
       </c>
       <c r="F102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかってたわ。もう追いつけないって</t>
+          <t xml:space="preserve">まだ使い道があるのね。いいわ、付き合ってあげる</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.normal.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.normal.seductive[1]</t>
+          <t xml:space="preserve">high_trust.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3643,14 +3643,14 @@
       </c>
       <c r="F103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンに引退ですって？ 冗談でしょう？</t>
+          <t xml:space="preserve">あなたがそう言うなら…もう少し頑張ってみるわ</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.normal.seductive[1]</t>
+          <t xml:space="preserve">accept_former_champ.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3675,14 +3675,14 @@
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を追い出すつもり？ そうはいかないわよ</t>
+          <t xml:space="preserve">最後にいい試合がしたいの。お願いできる？</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3692,12 +3692,12 @@
       </c>
       <c r="C105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.normal.seductive[1]</t>
+          <t xml:space="preserve">accept_heel.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3707,14 +3707,14 @@
       </c>
       <c r="F105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ終わらないわ。私はまだ闘えるの</t>
+          <t xml:space="preserve">ふふ…言われなくても辞めるつもりだったわ</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="C106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.normal.seductive[1]</t>
+          <t xml:space="preserve">accept_no_title.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3739,14 +3739,14 @@
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">引退ですって？ 次の興行を見てちょうだい</t>
+          <t xml:space="preserve">…わかったわ。潮時よね</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.normal.seductive[1]</t>
+          <t xml:space="preserve">accept_terminal.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3771,14 +3771,14 @@
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点からの景色…忘れないわ</t>
+          <t xml:space="preserve">…わかったわ。もう限界なのよね</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3788,12 +3788,12 @@
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.normal.seductive[1]</t>
+          <t xml:space="preserve">accept_winless.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3803,14 +3803,14 @@
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトには届かなかったわ。でも、後悔はないの</t>
+          <t xml:space="preserve">…わかってたわ。もう追いつけないって</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="C109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.normal.seductive[1]</t>
+          <t xml:space="preserve">refuse_champ.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3835,14 +3835,14 @@
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ…泣かないで。寂しくなるでしょう？</t>
+          <t xml:space="preserve">チャンピオンに引退ですって？ 冗談でしょう？</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3852,12 +3852,12 @@
       </c>
       <c r="C110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.normal.seductive[1]</t>
+          <t xml:space="preserve">refuse_distrust.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3867,14 +3867,14 @@
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここが、私の全てだったの</t>
+          <t xml:space="preserve">私を追い出すつもり？ そうはいかないわよ</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="C111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.normal.seductive[1]</t>
+          <t xml:space="preserve">refuse_fighting.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3899,14 +3899,14 @@
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ何も成し遂げてないのに…嘘でしょう…</t>
+          <t xml:space="preserve">まだ終わらないわ。私はまだ闘えるの</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3916,12 +3916,12 @@
       </c>
       <c r="C112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.normal.seductive[1]</t>
+          <t xml:space="preserve">refuse_heel.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3931,14 +3931,14 @@
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体がね…もう言うことを聞かないの…</t>
+          <t xml:space="preserve">引退ですって？ 次の興行を見てちょうだい</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.normal.seductive[1]</t>
+          <t xml:space="preserve">A1_champion.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3963,14 +3963,14 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わかってたわ。いつか来るって</t>
+          <t xml:space="preserve">頂点からの景色…忘れないわ</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.normal.seductive[1]</t>
+          <t xml:space="preserve">A2_uncrowned.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3995,14 +3995,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このベルト…まだ返したくなかったのに…</t>
+          <t xml:space="preserve">ベルトには届かなかったわ。でも、後悔はないの</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="C115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">A3_heel.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4027,14 +4027,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、他に行く場所なんてないわ。ここが好きなの</t>
+          <t xml:space="preserve">ふふ…泣かないで。寂しくなるでしょう？</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4044,29 +4044,29 @@
       </c>
       <c r="C116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.normal.seductive[1]</t>
+          <t xml:space="preserve">A4_veteran.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがと、社長♡ もっと頑張っちゃうからね。</t>
+          <t xml:space="preserve">ここが、私の全てだったの</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4076,29 +4076,29 @@
       </c>
       <c r="C117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.normal.seductive[1]</t>
+          <t xml:space="preserve">B1_young.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少しでも考えてくれたのね。…ありがと♡</t>
+          <t xml:space="preserve">まだ何も成し遂げてないのに…嘘でしょう…</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4108,29 +4108,29 @@
       </c>
       <c r="C118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.normal.seductive[1]</t>
+          <t xml:space="preserve">B2_prime.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう。残念ね。</t>
+          <t xml:space="preserve">体がね…もう言うことを聞かないの…</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4140,29 +4140,29 @@
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.normal.seductive[1]</t>
+          <t xml:space="preserve">B3_older.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、ちょっといい？ {tenure}{record}…もう少しだけ、考えてくれない？</t>
+          <t xml:space="preserve">わかってたわ。いつか来るって</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4172,29 +4172,29 @@
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.normal.seductive[1]</t>
+          <t xml:space="preserve">B4_champion_injury.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう。残念だけど…仕方ないわね。</t>
+          <t xml:space="preserve">このベルト…まだ返したくなかったのに…</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.normal.seductive[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4204,29 +4204,29 @@
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.normal.seductive[1]</t>
+          <t xml:space="preserve">normal.seductive[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">聞いてくれるの？ {record}…新しい場所で、自分を試してみたいの。</t>
+          <t xml:space="preserve">あら、他に行く場所なんてないわ。ここが好きなの</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.normal.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.normal.seductive[1]</t>
+          <t xml:space="preserve">raise_accept.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4251,14 +4251,14 @@
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長…ごめんなさい。{tenure}ここを離れたいの。</t>
+          <t xml:space="preserve">ありがと、社長♡ もっと頑張っちゃうからね。</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.normal.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.normal.seductive[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4283,14 +4283,14 @@
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう。{tenure_farewell}{rivalry}元気でね。</t>
+          <t xml:space="preserve">少しでも考えてくれたのね。…ありがと♡</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.normal.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.normal.seductive[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4315,14 +4315,14 @@
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう。でも…もう決めたの。ごめんね。</t>
+          <t xml:space="preserve">……そう。残念ね。</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.normal.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.normal.seductive[1]</t>
+          <t xml:space="preserve">raise_open.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4347,402 +4347,402 @@
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そこまでしてくれるの？ …もう少しだけ、いてあげる♡</t>
+          <t xml:space="preserve">社長、ちょっといい？ {tenure}{record}…もう少しだけ、考えてくれない？</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.normal.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_refuse.normal.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……そう。残念だけど…仕方ないわね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.normal.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長、手短に言うわ。辞めます。もう決めたの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.normal.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お世話になったわ。でも、もうここでは続けられないの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.normal.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_listen.normal.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">聞いてくれるの？ {record}…新しい場所で、自分を試してみたいの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.normal.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.normal.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長…ごめんなさい。{tenure}ここを離れたいの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.normal.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.normal.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……そう。{tenure_farewell}{rivalry}元気でね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="40" customHeight="1">
+      <c r="A132" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.normal.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.normal.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ありがとう。でも…もう決めたの。ごめんね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.normal.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.normal.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……そこまでしてくれるの？ …もう少しだけ、いてあげる♡</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="40" customHeight="1">
+      <c r="A134" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.normal.seductive[1]</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr" s="2">
+      <c r="B134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr" s="12">
+      <c r="D134" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.normal.seductive[1]</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr" s="2">
+      <c r="E134" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr" s="3">
+      <c r="F134" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">うれしいお誘いだけど…今の仲間を置いていく気にはなれないわ。
 ごめんなさい</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="40" customHeight="1">
-      <c r="A127" t="inlineStr" s="15">
+    <row r="135" ht="40" customHeight="1">
+      <c r="A135" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.fail.normal.seductive[1]</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr" s="2">
+      <c r="B135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr" s="12">
+      <c r="D135" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fail.normal.seductive[1]</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr" s="2">
+      <c r="E135" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr" s="3">
+      <c r="F135" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ごめんなさい、今回はパス。
 縁があればまたね</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="40" customHeight="1">
-      <c r="A128" t="inlineStr" s="15">
+    <row r="136" ht="40" customHeight="1">
+      <c r="A136" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.start.normal.seductive[1]</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr" s="2">
+      <c r="B136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr" s="12">
+      <c r="D136" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">start.normal.seductive[1]</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr" s="2">
+      <c r="E136" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr" s="3">
+      <c r="F136" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">私を誘うの？
 ふふ…条件次第ね</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="40" customHeight="1">
-      <c r="A129" t="inlineStr" s="15">
+    <row r="137" ht="40" customHeight="1">
+      <c r="A137" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.success.normal.seductive[1]</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr" s="2">
+      <c r="B137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr" s="12">
+      <c r="D137" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">success.normal.seductive[1]</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr" s="2">
+      <c r="E137" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr" s="3">
+      <c r="F137" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…わかったわ、行く。
 実力で居場所を作ってみせるわ</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="40" customHeight="1">
-      <c r="A130" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.normal.seductive[1]</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">あら…何かが変わった気がするわ</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="40" customHeight="1">
-      <c r="A131" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">BT_HINT_LINES.normal.seductive[1]</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">何かが変わり始めてる…自分でもわかるわ</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="40" customHeight="1">
-      <c r="A132" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.normal.seductive[1]</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">cap_reached.normal.seductive[1]</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">これ以上は…ね。でも、十分よ</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="40" customHeight="1">
-      <c r="A133" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.normal.seductive[1]</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ovr_elite.normal.seductive[1]</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ここまで来ちゃったのね…ふふ</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="40" customHeight="1">
-      <c r="A134" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.normal.seductive[1]</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ovr_growth.normal.seductive[1]</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ふふ、ちょっとは良くなったかしら</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="40" customHeight="1">
-      <c r="A135" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.normal.seductive[1]</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ovr_legend.normal.seductive[1]</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ここまで来たら…もう怖いものなんてないわ</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="40" customHeight="1">
-      <c r="A136" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.normal.seductive[1]</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">pop_growth.normal.seductive[1]</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ふふ、注目されるのは悪くないわね</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="40" customHeight="1">
-      <c r="A137" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.normal.seductive[1]</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">pop_star.normal.seductive[1]</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">こんなにたくさん…みんなの視線が気持ちいいわ</t>
-        </is>
-      </c>
-    </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="12">
@@ -4767,14 +4767,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何のために闘ってるのかしら…わからなくなったわ</t>
+          <t xml:space="preserve">あら…何かが変わった気がするわ</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="12">
@@ -4799,14 +4799,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだやれるわ…やってみせる</t>
+          <t xml:space="preserve">何かが変わり始めてる…自分でもわかるわ</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4816,12 +4816,12 @@
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">cap_reached.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4831,14 +4831,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっと…戻ってこれたわ</t>
+          <t xml:space="preserve">これ以上は…ね。でも、十分よ</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.normal.seductive[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.normal.seductive[1]</t>
+          <t xml:space="preserve">ovr_elite.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4863,14 +4863,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの負けから…何かがおかしいの</t>
+          <t xml:space="preserve">ここまで来ちゃったのね…ふふ</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.normal.seductive[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4880,12 +4880,12 @@
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.normal.seductive[1]</t>
+          <t xml:space="preserve">ovr_growth.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4895,14 +4895,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体は治ったはずなのに…ね、動けないの</t>
+          <t xml:space="preserve">ふふ、ちょっとは良くなったかしら</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.normal.seductive[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.normal.seductive[1]</t>
+          <t xml:space="preserve">ovr_legend.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4927,14 +4927,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">戻ってこれたのに…怖いの</t>
+          <t xml:space="preserve">ここまで来たら…もう怖いものなんてないわ</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.normal.seductive[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4944,12 +4944,12 @@
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.normal.seductive[1]</t>
+          <t xml:space="preserve">pop_growth.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4959,14 +4959,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我は治ったのに…気力が戻らないの</t>
+          <t xml:space="preserve">ふふ、注目されるのは悪くないわね</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.normal.seductive[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4976,29 +4976,29 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.normal.seductive[1]</t>
+          <t xml:space="preserve">pop_star.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高に痺れたわ。…また味わいたい、あの感覚</t>
+          <t xml:space="preserve">こんなにたくさん…みんなの視線が気持ちいいわ</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.normal.seductive[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -5008,29 +5008,29 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.seductive[1]</t>
+          <t xml:space="preserve">normal.seductive[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この輝き、よく似合うでしょう？ 欲しいなら…奪いに来なさい</t>
+          <t xml:space="preserve">何のために闘ってるのかしら…わからなくなったわ</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.normal.seductive[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5040,29 +5040,29 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.normal.seductive[1]</t>
+          <t xml:space="preserve">normal.seductive[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">素敵な花道を用意してくれるのね。…ありがとう。最高の舞台だったわ</t>
+          <t xml:space="preserve">まだやれるわ…やってみせる</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.normal.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5072,29 +5072,29 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.normal.seductive[1]</t>
+          <t xml:space="preserve">normal.seductive[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、私の魅力が伝わったかしら</t>
+          <t xml:space="preserve">やっと…戻ってこれたわ</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.normal.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5104,29 +5104,29 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.normal.seductive[1]</t>
+          <t xml:space="preserve">defeat.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一年間ずっと見ていてくれたでしょう？ …ちゃんと応えたわ</t>
+          <t xml:space="preserve">あの負けから…何かがおかしいの</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.normal.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5136,29 +5136,29 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.normal.seductive[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">覚えておいて。この名前、来年はもっと大きなところで呼ばれるから</t>
+          <t xml:space="preserve">体は治ったはずなのに…ね、動けないの</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5168,29 +5168,29 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふっ、いよいよドームね</t>
+          <t xml:space="preserve">戻ってこれたのに…怖いの</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.seductive[2]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5200,29 +5200,29 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[2]</t>
+          <t xml:space="preserve">penalty_end.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この大舞台で…見せたいものがあるの</t>
+          <t xml:space="preserve">怪我は治ったのに…気力が戻らないの</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.seductive[3]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[3]</t>
+          <t xml:space="preserve">bestMatch.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5247,14 +5247,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドームのお客様を…虜にしてあげる</t>
+          <t xml:space="preserve">最高に痺れたわ。…また味わいたい、あの感覚</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5264,12 +5264,12 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">champion.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5279,14 +5279,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員のお客様…今夜の私に、酔いしれてくれたのね</t>
+          <t xml:space="preserve">この輝き、よく似合うでしょう？ 欲しいなら…奪いに来なさい</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.seductive[2]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[2]</t>
+          <t xml:space="preserve">hallOfFame.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5311,14 +5311,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ…この達成感、格別ね</t>
+          <t xml:space="preserve">素敵な花道を用意してくれるのね。…ありがとう。最高の舞台だったわ</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.seductive[3]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[3]</t>
+          <t xml:space="preserve">mediaAward.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5343,14 +5343,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">忘れられない夜になったわ</t>
+          <t xml:space="preserve">ふふ、私の魅力が伝わったかしら</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.normal.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5360,29 +5360,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.normal.seductive[1]</t>
+          <t xml:space="preserve">mvp.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近、体が素直に動いてくれるの。嬉しいわ</t>
+          <t xml:space="preserve">一年間ずっと見ていてくれたでしょう？ …ちゃんと応えたわ</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.normal.seductive[2]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5392,29 +5392,29 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.normal.seductive[2]</t>
+          <t xml:space="preserve">rookie.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習が楽しくなってきた気がする</t>
+          <t xml:space="preserve">覚えておいて。この名前、来年はもっと大きなところで呼ばれるから</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.normal.seductive[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5424,29 +5424,29 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.normal.seductive[1]</t>
+          <t xml:space="preserve">normal.seductive[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい仲間に恵まれたわ。心強いの</t>
+          <t xml:space="preserve">ふふっ、いよいよドームね</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.normal.seductive[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.seductive[2]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5456,29 +5456,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.normal.seductive[1]</t>
+          <t xml:space="preserve">normal.seductive[2]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少し疲れただけよ。心配しないで</t>
+          <t xml:space="preserve">この大舞台で…見せたいものがあるの</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.normal.seductive[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.seductive[3]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5488,29 +5488,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.normal.seductive[1]</t>
+          <t xml:space="preserve">normal.seductive[3]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなに応援してもらえるなんて…嬉しいわ</t>
+          <t xml:space="preserve">ドームのお客様を…虜にしてあげる</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.normal.seductive[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5520,29 +5520,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.normal.seductive[1]</t>
+          <t xml:space="preserve">normal.seductive[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もういいわ。分かったから</t>
+          <t xml:space="preserve">満員のお客様…今夜の私に、酔いしれてくれたのね</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.normal.seductive[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.seductive[2]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5552,29 +5552,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.normal.seductive[1]</t>
+          <t xml:space="preserve">normal.seductive[2]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい、ちょっと考え事してて</t>
+          <t xml:space="preserve">うふふ…この達成感、格別ね</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.normal.seductive[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.seductive[3]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5584,29 +5584,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.normal.seductive[1]</t>
+          <t xml:space="preserve">normal.seductive[3]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら……ずいぶん安く見られたものね</t>
+          <t xml:space="preserve">忘れられない夜になったわ</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.normal.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5616,29 +5616,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.normal.seductive[1]</t>
+          <t xml:space="preserve">N1.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、嬉しい。ありがとう</t>
+          <t xml:space="preserve">最近、体が素直に動いてくれるの。嬉しいわ</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.normal.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.normal.seductive[2]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5648,29 +5648,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.normal.seductive[1]</t>
+          <t xml:space="preserve">N1.normal.seductive[2]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合宿ね。しっかり鍛えるわ</t>
+          <t xml:space="preserve">練習が楽しくなってきた気がする</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.normal.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5680,29 +5680,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.normal.seductive[1]</t>
+          <t xml:space="preserve">N2.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと見てくれてたのね…嬉しい。頑張るわ</t>
+          <t xml:space="preserve">いい仲間に恵まれたわ。心強いの</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.normal.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5712,29 +5712,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.normal.seductive[1]</t>
+          <t xml:space="preserve">N3.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。もう少し、頑張ってみるわ</t>
+          <t xml:space="preserve">少し疲れただけよ。心配しないで</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.normal.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5744,29 +5744,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.normal.seductive[1]</t>
+          <t xml:space="preserve">N4.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">メディア出演…？ 楽しみだわ</t>
+          <t xml:space="preserve">こんなに応援してもらえるなんて…嬉しいわ</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.normal.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5776,29 +5776,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.normal.seductive[1]</t>
+          <t xml:space="preserve">N5_low.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しかったわ。こういう時間もいいわね</t>
+          <t xml:space="preserve">…もういいわ。分かったから</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.normal.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5808,29 +5808,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.normal.seductive[1]</t>
+          <t xml:space="preserve">N5_warning.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう。リフレッシュしてくるわね</t>
+          <t xml:space="preserve">…ごめんなさい、ちょっと考え事してて</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.normal.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.normal.seductive[1]</t>
+          <t xml:space="preserve">bonus_insult.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5855,14 +5855,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">しっかり吸収させてもらうわね</t>
+          <t xml:space="preserve">あら……ずいぶん安く見られたものね</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.normal.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5872,12 +5872,12 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.normal.seductive[1]</t>
+          <t xml:space="preserve">bonus.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5887,14 +5887,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">メディア出演のお話？ 楽しみだわ</t>
+          <t xml:space="preserve">あら、嬉しい。ありがとう</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.normal.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.normal.seductive[1]</t>
+          <t xml:space="preserve">camp.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5919,14 +5919,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">他の団体からお誘いが来てるの</t>
+          <t xml:space="preserve">合宿ね。しっかり鍛えるわ</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.normal.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.normal.seductive[1]</t>
+          <t xml:space="preserve">encourage_high_trust.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5951,14 +5951,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさいね…今日はちょっと、気持ちが入らなくて</t>
+          <t xml:space="preserve">ずっと見てくれてたのね…嬉しい。頑張るわ</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.normal.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.normal.seductive[1]</t>
+          <t xml:space="preserve">encourage.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5983,14 +5983,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（「最近、ここにいる意味あるのかしら」と同僚に漏らしている）</t>
+          <t xml:space="preserve">…ありがとう。もう少し、頑張ってみるわ</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.normal.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.normal.seductive[1]</t>
+          <t xml:space="preserve">media.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -6015,14 +6015,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「次のステージが待っているかも」と匂わせ投稿）</t>
+          <t xml:space="preserve">メディア出演…？ 楽しみだわ</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.normal.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.normal.seductive[1]</t>
+          <t xml:space="preserve">party.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6047,14 +6047,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">タイトルマッチの機会、いただけないかしら</t>
+          <t xml:space="preserve">楽しかったわ。こういう時間もいいわね</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.normal.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6064,12 +6064,12 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.normal.seductive[1]</t>
+          <t xml:space="preserve">refresh_leave.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6079,14 +6079,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人との試合、組んでもらえないかしら</t>
+          <t xml:space="preserve">ありがとう。リフレッシュしてくるわね</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.normal.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6096,12 +6096,12 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.normal.seductive[1]</t>
+          <t xml:space="preserve">special_treatment.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6111,14 +6111,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少し休ませてもらえないかしら…</t>
+          <t xml:space="preserve">ありがとう。早く戻れるように頑張るわ</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.normal.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.normal.seductive[1]</t>
+          <t xml:space="preserve">trainer.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6143,14 +6143,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このままじゃ困るわ。ちゃんと考えてもらえないかしら</t>
+          <t xml:space="preserve">しっかり吸収させてもらうわね</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.normal.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.normal.seductive[1]</t>
+          <t xml:space="preserve">E1.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6175,14 +6175,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">特訓させてもらえないかしら？</t>
+          <t xml:space="preserve">メディア出演のお話？ 楽しみだわ</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.normal.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.normal.seductive[1]</t>
+          <t xml:space="preserve">E4.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6207,14 +6207,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の指導、私にやらせてもらえないかしら</t>
+          <t xml:space="preserve">新しいスカウトのお話が来てるみたいよ</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.normal.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.normal.seductive[1]</t>
+          <t xml:space="preserve">E6.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6239,14 +6239,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し時間がかかりそう。ごめんなさいね</t>
+          <t xml:space="preserve">他の団体からお誘いが来てるの</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.normal.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.normal.seductive[1]</t>
+          <t xml:space="preserve">S_boycott.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6271,14 +6271,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人とはもう無理よ。何とかしてもらえないかしら</t>
+          <t xml:space="preserve">ごめんなさいね…今日はちょっと、気持ちが入らなくて</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.normal.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.normal.seductive[1]</t>
+          <t xml:space="preserve">S_grumble.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6303,14 +6303,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">向こうにも非があるのに…私だけが悪いの？</t>
+          <t xml:space="preserve">（「最近、ここにいる意味あるのかしら」と同僚に漏らしている）</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.normal.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.normal.seductive[1]</t>
+          <t xml:space="preserve">S_sns.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6335,14 +6335,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私のイメージに合うブランドね。いい選択だわ♡</t>
+          <t xml:space="preserve">（SNSに「次のステージが待っているかも」と匂わせ投稿）</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.normal.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6352,12 +6352,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.normal.seductive[1]</t>
+          <t xml:space="preserve">S1.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6367,14 +6367,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">カメラの前ね…いい絵、撮らせてあげる♡</t>
+          <t xml:space="preserve">タイトルマッチの機会、いただけないかしら</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.normal.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.normal.seductive[1]</t>
+          <t xml:space="preserve">S2.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6399,14 +6399,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンと直接会える機会ね…喜ばせてあげるわ♡</t>
+          <t xml:space="preserve">あの人との試合、組んでもらえないかしら</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.normal.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.normal.seductive[1]</t>
+          <t xml:space="preserve">S3.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6431,14 +6431,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ランウェイか…私の本領発揮ね♡</t>
+          <t xml:space="preserve">少し休ませてもらえないかしら…</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.normal.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.normal.seductive[1]</t>
+          <t xml:space="preserve">S4_direct.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6463,14 +6463,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">グラビアね…全部見せてあげるわ♡</t>
+          <t xml:space="preserve">このままじゃ困るわ。ちゃんと考えてもらえないかしら</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.normal.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6480,12 +6480,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.normal.seductive[1]</t>
+          <t xml:space="preserve">S4_silent.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6495,14 +6495,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バラエティか。じゃあ、素の私を少し見せてあげようかな</t>
+          <t xml:space="preserve">…（沈黙）…ううん、なんでもないの</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.normal.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.normal.seductive[1]</t>
+          <t xml:space="preserve">S5.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6527,14 +6527,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">取材ね…いい姿を見せてあげるわ</t>
+          <t xml:space="preserve">特訓させてもらえないかしら？</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6544,29 +6544,29 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">S6.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでくれるなら…期待に応えるわよ</t>
+          <t xml:space="preserve">後輩の指導、私にやらせてもらえないかしら</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6576,29 +6576,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">B1.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくね。期待に応えてあげる</t>
+          <t xml:space="preserve">…少し時間がかかりそう。ごめんなさいね</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.seductive[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6608,29 +6608,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[2]</t>
+          <t xml:space="preserve">B2_fighter1.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、選んでくれてありがとう</t>
+          <t xml:space="preserve">あの人とはもう無理よ。何とかしてもらえないかしら</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6640,29 +6640,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">B2_fighter2.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくね。力になるわ</t>
+          <t xml:space="preserve">向こうにも非があるのに…私だけが悪いの？</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6672,29 +6672,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">B4_brand.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくね。精一杯やるわ</t>
+          <t xml:space="preserve">私のイメージに合うブランドね。いい選択だわ♡</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6704,29 +6704,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">B4_cm.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ちょっとだけ、休ませてね</t>
+          <t xml:space="preserve">カメラの前ね…いい絵、撮らせてあげる♡</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.normal.seductive[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6736,29 +6736,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[2]</t>
+          <t xml:space="preserve">B4_fan.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すぐに戻るわ。待っててくれる？</t>
+          <t xml:space="preserve">ファンと直接会える機会ね…喜ばせてあげるわ♡</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.normal.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6768,29 +6768,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.normal.seductive[1]</t>
+          <t xml:space="preserve">B4_fashion.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでくれるなら…期待に応えるわよ</t>
+          <t xml:space="preserve">ランウェイか…私の本領発揮ね♡</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6800,29 +6800,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.normal.seductive[1]</t>
+          <t xml:space="preserve">B4_gravure.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくね。期待に応えてあげる</t>
+          <t xml:space="preserve">グラビアね…全部見せてあげるわ♡</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.seductive[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6832,29 +6832,29 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.normal.seductive[2]</t>
+          <t xml:space="preserve">B4_variety.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、選んでくれてありがとう</t>
+          <t xml:space="preserve">バラエティか。じゃあ、素の私を少し見せてあげようかな</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.normal.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6864,29 +6864,29 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.normal.seductive[1]</t>
+          <t xml:space="preserve">B4.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくね。力になるわ</t>
+          <t xml:space="preserve">取材ね…いい姿を見せてあげるわ</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6896,12 +6896,12 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.normal.seductive[1]</t>
+          <t xml:space="preserve">normal.seductive[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6911,14 +6911,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくね。精一杯やるわ</t>
+          <t xml:space="preserve">選んでくれるなら…期待に応えるわよ</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.normal.seductive[1]</t>
+          <t xml:space="preserve">normal.seductive[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6943,14 +6943,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ちょっとだけ、休ませてね</t>
+          <t xml:space="preserve">よろしくね。期待に応えてあげる</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.seductive[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.seductive[2]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.normal.seductive[2]</t>
+          <t xml:space="preserve">normal.seductive[2]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6975,14 +6975,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すぐに戻るわ。待っててくれる？</t>
+          <t xml:space="preserve">ふふ、選んでくれてありがとう</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6992,12 +6992,12 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.normal.seductive[1]</t>
+          <t xml:space="preserve">normal.seductive[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -7007,14 +7007,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここでの思い出、大切にするわ</t>
+          <t xml:space="preserve">よろしくね。力になるわ</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.seductive[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.normal.seductive[2]</t>
+          <t xml:space="preserve">normal.seductive[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7039,14 +7039,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お世話になりました。また、どこかで</t>
+          <t xml:space="preserve">よろしくね。精一杯やるわ</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7056,12 +7056,12 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.normal.seductive[1]</t>
+          <t xml:space="preserve">normal.seductive[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7071,14 +7071,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間だけど、よろしくね</t>
+          <t xml:space="preserve">…ちょっとだけ、休ませてね</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.normal.seductive[2]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7088,12 +7088,12 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.normal.seductive[1]</t>
+          <t xml:space="preserve">normal.seductive[2]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7103,14 +7103,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいわ…でも、次こそはね</t>
+          <t xml:space="preserve">すぐに戻るわ。待っててくれる？</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.normal.seductive[1]</t>
+          <t xml:space="preserve">draftInterest.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7135,14 +7135,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛成功…。このベルト、まだ返す気はないわ</t>
+          <t xml:space="preserve">選んでくれるなら…期待に応えるわよ</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.normal.seductive[1]</t>
+          <t xml:space="preserve">draftJoin.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7167,14 +7167,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトがない景色なんて…でも、ここで終わらないわ</t>
+          <t xml:space="preserve">よろしくね。期待に応えてあげる</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.seductive[2]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.normal.seductive[1]</t>
+          <t xml:space="preserve">draftJoin.normal.seductive[2]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7199,14 +7199,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオン…最高の気分ね</t>
+          <t xml:space="preserve">ふふ、選んでくれてありがとう</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">faGreeting.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7231,14 +7231,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここでの思い出、大切にするわ</t>
+          <t xml:space="preserve">落ちこぼれを拾うなんて。…物好きね。</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[2]</t>
+          <t xml:space="preserve">faSigning.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7263,14 +7263,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お世話になりました。また、どこかで</t>
+          <t xml:space="preserve">よろしくね。力になるわ</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7280,12 +7280,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">faWelcome.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7295,14 +7295,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間だけど、よろしくね</t>
+          <t xml:space="preserve">よろしくね。精一杯やるわ</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7312,12 +7312,12 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">injury.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7327,14 +7327,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいわ…でも、次こそはね</t>
+          <t xml:space="preserve">…ちょっとだけ、休ませてね</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.seductive[2]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">injury.normal.seductive[2]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7359,14 +7359,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛成功…。このベルト、まだ返す気はないわ</t>
+          <t xml:space="preserve">すぐに戻るわ。待っててくれる？</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7376,12 +7376,12 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">release.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7391,14 +7391,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトがない景色なんて…でも、ここで終わらないわ</t>
+          <t xml:space="preserve">ここでの思い出、大切にするわ</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.seductive[2]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">release.normal.seductive[2]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7423,14 +7423,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオン…最高の気分ね</t>
+          <t xml:space="preserve">お世話になりました。また、どこかで</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7440,29 +7440,29 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.normal.seductive[1]</t>
+          <t xml:space="preserve">rentalGreeting.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう…合わないみたいね</t>
+          <t xml:space="preserve">短い間だけど、よろしくね</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7472,29 +7472,29 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.normal.seductive[1]</t>
+          <t xml:space="preserve">scoutGreeting.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近どこか冷たいわ…気のせいかしら</t>
+          <t xml:space="preserve">目をつけたのはそっち。…責任、取ってね</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7504,29 +7504,29 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.normal.seductive[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なかなか面白い人ね。もっと近くで見ていたい</t>
+          <t xml:space="preserve">悔しいわ…でも、次こそはね</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7536,29 +7536,29 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.normal.seductive[1]</t>
+          <t xml:space="preserve">titleDefense.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">特別な存在。他の誰とも違うの</t>
+          <t xml:space="preserve">防衛成功…。このベルト、まだ返す気はないわ</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7568,29 +7568,29 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.normal.seductive[1]</t>
+          <t xml:space="preserve">titleLoss.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もういいかしら。次を探さなきゃ</t>
+          <t xml:space="preserve">ベルトがない景色なんて…でも、ここで終わらないわ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7600,29 +7600,29 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.normal.seductive[1]</t>
+          <t xml:space="preserve">titleWin.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気になるわ…潰しがいがありそうね</t>
+          <t xml:space="preserve">チャンピオン…最高の気分ね</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7632,29 +7632,29 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.normal.seductive[1]</t>
+          <t xml:space="preserve">normal.seductive[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうしても許せない。必ず私が勝つわ</t>
+          <t xml:space="preserve">ここでの思い出、大切にするわ</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.seductive[2]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7664,29 +7664,29 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.normal.seductive[1]</t>
+          <t xml:space="preserve">normal.seductive[2]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私の全て…最高の獲物よ</t>
+          <t xml:space="preserve">お世話になりました。また、どこかで</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7696,29 +7696,29 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.normal.seductive[1]</t>
+          <t xml:space="preserve">normal.seductive[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここでなら…私らしくいられるわ</t>
+          <t xml:space="preserve">短い間だけど、よろしくね</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7728,29 +7728,29 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.normal.seductive[1]</t>
+          <t xml:space="preserve">normal.seductive[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここにはもう何も残ってないわ</t>
+          <t xml:space="preserve">悔しいわ…でも、次こそはね</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7760,29 +7760,29 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.normal.seductive[1]</t>
+          <t xml:space="preserve">normal.seductive[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここにいる意味…本当にあるのかしら</t>
+          <t xml:space="preserve">防衛成功…。このベルト、まだ返す気はないわ</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7792,29 +7792,29 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.normal.seductive[1]</t>
+          <t xml:space="preserve">normal.seductive[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けは負け。でも…悪くない戦いだったわ</t>
+          <t xml:space="preserve">ベルトがない景色なんて…でも、ここで終わらないわ</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7824,29 +7824,29 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.normal.seductive[1]</t>
+          <t xml:space="preserve">normal.seductive[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">完璧な夜ね…最高の気分だわ</t>
+          <t xml:space="preserve">チャンピオン…最高の気分ね</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.normal.seductive[1]</t>
+          <t xml:space="preserve">bond_39_down.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7871,14 +7871,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたのね…屈辱だわ</t>
+          <t xml:space="preserve">もう…合わないみたいね</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7888,12 +7888,12 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.normal.seductive[1]</t>
+          <t xml:space="preserve">bond_59_down.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7903,14 +7903,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、今日も勝ち。気分がいいわ</t>
+          <t xml:space="preserve">最近どこか冷たいわ…気のせいかしら</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.normal.seductive[1]</t>
+          <t xml:space="preserve">bond_60_up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7935,14 +7935,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">汗を流すのも悪くないわね</t>
+          <t xml:space="preserve">なかなか面白い人ね。もっと近くで見ていたい</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7952,12 +7952,12 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.normal.seductive[1]</t>
+          <t xml:space="preserve">bond_80_up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7967,14 +7967,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ねぇ…最近私のこと放置してない？</t>
+          <t xml:space="preserve">特別な存在。他の誰とも違うの</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.normal.seductive[1]</t>
+          <t xml:space="preserve">rivalry_29_down.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7999,14 +7999,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近いい扱い受けてる気がするわ。嬉しいわね</t>
+          <t xml:space="preserve">もういいかしら。次を探さなきゃ</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.normal.seductive[1]</t>
+          <t xml:space="preserve">rivalry_30_up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8031,14 +8031,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと気になってるの。いい距離感よね</t>
+          <t xml:space="preserve">気になるわ…潰しがいがありそうね</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.normal.seductive[1]</t>
+          <t xml:space="preserve">rivalry_50_up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8063,14 +8063,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…考えちゃうのよね</t>
+          <t xml:space="preserve">どうしても許せない。必ず私が勝つわ</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.normal.seductive[1]</t>
+          <t xml:space="preserve">rivalry_70_up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8095,14 +8095,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を干すつもり？ もったいないと思うけど</t>
+          <t xml:space="preserve">私の全て…最高の獲物よ</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.normal.seductive[1]</t>
+          <t xml:space="preserve">trust_above_75.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8127,14 +8127,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体が言うこと聞かないわ…もどかしい</t>
+          <t xml:space="preserve">ここでなら…私らしくいられるわ</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.normal.seductive[1]</t>
+          <t xml:space="preserve">trust_below_20.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8159,14 +8159,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負け続き…こんなの私じゃないわ</t>
+          <t xml:space="preserve">ここにはもう何も残ってないわ</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.normal.seductive[1]</t>
+          <t xml:space="preserve">trust_below_35.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8191,14 +8191,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近負けなしよ。ふふ、誰が相手でも返り討ちだわ</t>
+          <t xml:space="preserve">ここにいる意味…本当にあるのかしら</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.normal.seductive[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8223,14 +8223,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">退屈…早くリングに立ちたいわ</t>
+          <t xml:space="preserve">負けは負け。でも…悪くない戦いだったわ</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.normal.seductive[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8255,14 +8255,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いたわね、そういえば。……それだけよ</t>
+          <t xml:space="preserve">完璧な夜ね…最高の気分だわ</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8272,12 +8272,12 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">GL-01.loss.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8287,14 +8287,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、いつもの私に戻ったみたい。でも悪くない気分よ</t>
+          <t xml:space="preserve">負けたのね…屈辱だわ</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8304,29 +8304,29 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.seductive[1]</t>
+          <t xml:space="preserve">GL-01.win.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体、まだ震えてるの。でも…この傷ごと、最後の舞台に上がるわ</t>
+          <t xml:space="preserve">ふふ、今日も勝ち。気分がいいわ</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8336,29 +8336,29 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.seductive[2]</t>
+          <t xml:space="preserve">GL-02.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぼろぼろでしょ、私。でもね…一番きれいに終わらせるのは、こういう時よ</t>
+          <t xml:space="preserve">汗を流すのも悪くないわね</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8368,29 +8368,29 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.seductive[1]</t>
+          <t xml:space="preserve">GL-03.down.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">来るなら誰でもいいわ。全部、受け止めてあげる</t>
+          <t xml:space="preserve">ねぇ…最近私のこと放置してない？</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8400,29 +8400,29 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.seductive[2]</t>
+          <t xml:space="preserve">GL-03.up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この一戦、たっぷり付き合ってもらうわよ。逃がさないから</t>
+          <t xml:space="preserve">最近いい扱い受けてる気がするわ。嬉しいわね</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8432,29 +8432,29 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.normal.seductive[1]</t>
+          <t xml:space="preserve">GL-04.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、落としたわ。…息、荒いでしょ? でも、まだ物足りないの。次、出してよ</t>
+          <t xml:space="preserve">ちょっと気になってるの。いい距離感よね</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8464,29 +8464,29 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.normal.seductive[2]</t>
+          <t xml:space="preserve">GL-05.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってるの。次の子、早くいらっしゃい。ここは、渡さないから</t>
+          <t xml:space="preserve">…考えちゃうのよね</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8496,29 +8496,29 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.seductive[1]</t>
+          <t xml:space="preserve">GL-06.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で勝ったのよ。この勝利は、一人じゃ味わえない特別なもの</t>
+          <t xml:space="preserve">私を干すつもり？ もったいないと思うけど</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8528,29 +8528,29 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.seductive[2]</t>
+          <t xml:space="preserve">GL-07.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が繋いでくれた……その信頼に応えられたなら、嬉しいわ</t>
+          <t xml:space="preserve">体が言うこと聞かないわ…もどかしい</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8560,29 +8560,29 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.normal.seductive[1]</t>
+          <t xml:space="preserve">GL-08.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">個人賞……嬉しくないとは言わない。でも、欲しかったのはこれじゃないの</t>
+          <t xml:space="preserve">負け続き…こんなの私じゃないわ</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8592,29 +8592,29 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.normal.seductive[2]</t>
+          <t xml:space="preserve">GL-09.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次は団体ごと勝つわ。そうでなきゃ……意味がないもの</t>
+          <t xml:space="preserve">最近負けなしよ。ふふ、誰が相手でも返り討ちだわ</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8624,29 +8624,29 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.normal.seductive[1]</t>
+          <t xml:space="preserve">GL-10.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ震えてるの、身体。でもね、この汗と痛みが……今日の私を証明してくれてる</t>
+          <t xml:space="preserve">退屈…早くリングに立ちたいわ</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8656,29 +8656,29 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.normal.seductive[2]</t>
+          <t xml:space="preserve">GL-11.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">倒しても倒しても来るの。でも、最後に立ってたのはこっち。悪くないでしょ？</t>
+          <t xml:space="preserve">いたわね、そういえば。……それだけよ</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8688,29 +8688,29 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.seductive[1]</t>
+          <t xml:space="preserve">normal.seductive[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝。…最高の気分ね</t>
+          <t xml:space="preserve">あら、いつもの私に戻ったみたい。でも悪くない気分よ</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.normal.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8720,12 +8720,12 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.seductive[2]</t>
+          <t xml:space="preserve">preFinal.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8735,14 +8735,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、これで終わりじゃないわよ</t>
+          <t xml:space="preserve">身体、まだ震えてるの。でも…この傷ごと、最後の舞台に上がるわ</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.normal.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.seductive[2]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8752,12 +8752,12 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.normal.seductive[1]</t>
+          <t xml:space="preserve">preFinal.normal.seductive[2]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8767,14 +8767,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、残念ね。でも次があるわ</t>
+          <t xml:space="preserve">ぼろぼろでしょ、私。でもね…一番きれいに終わらせるのは、こういう時よ</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.normal.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.normal.seductive[2]</t>
+          <t xml:space="preserve">preMatch.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8799,14 +8799,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいけど…いい経験だったわ</t>
+          <t xml:space="preserve">来るなら誰でもいいわ。全部、受け止めてあげる</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.normal.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.seductive[2]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8816,12 +8816,12 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.normal.seductive[1]</t>
+          <t xml:space="preserve">preMatch.normal.seductive[2]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8831,14 +8831,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、まずは一勝ね。次も魅せてあげるわ</t>
+          <t xml:space="preserve">この一戦、たっぷり付き合ってもらうわよ。逃がさないから</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.normal.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8848,12 +8848,12 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.normal.seductive[2]</t>
+          <t xml:space="preserve">survivor.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8863,14 +8863,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てたわ。……でもまだ先がある</t>
+          <t xml:space="preserve">一人、落としたわ。…息、荒いでしょ? でも、まだ物足りないの。次、出してよ</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.normal.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.seductive[2]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.normal.seductive[1]</t>
+          <t xml:space="preserve">survivor.normal.seductive[2]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8895,14 +8895,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい経験だったわ。もっと魅せられるようになりたいわね</t>
+          <t xml:space="preserve">まだ立ってるの。次の子、早くいらっしゃい。ここは、渡さないから</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.normal.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.normal.seductive[2]</t>
+          <t xml:space="preserve">champion.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8927,14 +8927,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだこんなものじゃないわよ</t>
+          <t xml:space="preserve">三人で勝ったのよ。この勝利は、一人じゃ味わえない特別なもの</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.normal.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.seductive[2]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8944,12 +8944,12 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.seductive[1]</t>
+          <t xml:space="preserve">champion.normal.seductive[2]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8959,14 +8959,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝…。最後の舞台、最高に魅せてあげるわ</t>
+          <t xml:space="preserve">仲間が繋いでくれた……その信頼に応えられたなら、嬉しいわ</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.normal.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8976,12 +8976,12 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.seductive[2]</t>
+          <t xml:space="preserve">defiant.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8991,14 +8991,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あと一つ。全てを懸けるわ</t>
+          <t xml:space="preserve">個人賞……嬉しくないとは言わない。でも、欲しかったのはこれじゃないの</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.normal.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.seductive[2]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.seductive[1]</t>
+          <t xml:space="preserve">defiant.normal.seductive[2]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9023,14 +9023,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次の相手…楽しみね</t>
+          <t xml:space="preserve">次は団体ごと勝つわ。そうでなきゃ……意味がないもの</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.normal.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9040,12 +9040,12 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.seductive[2]</t>
+          <t xml:space="preserve">gauntlet.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9055,14 +9055,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしの魅力、見せつけてあげる</t>
+          <t xml:space="preserve">まだ震えてるの、身体。でもね、この汗と痛みが……今日の私を証明してくれてる</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.normal.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.seductive[2]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.normal.seductive[1]</t>
+          <t xml:space="preserve">gauntlet.normal.seductive[2]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9087,14 +9087,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">出場が決まったわ。見ていてね</t>
+          <t xml:space="preserve">倒しても倒しても来るの。でも、最後に立ってたのはこっち。悪くないでしょ？</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.normal.seductive[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.normal.seductive[2]</t>
+          <t xml:space="preserve">champion.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9119,14 +9119,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">素敵な舞台ね。魅せてあげるわ</t>
+          <t xml:space="preserve">優勝。…最高の気分ね</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.normal.seductive[2]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">champion.normal.seductive[2]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9151,14 +9151,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は負けるわけにはいかないの。覚悟してね</t>
+          <t xml:space="preserve">ふふ、これで終わりじゃないわよ</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9168,12 +9168,12 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">postLose.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9183,14 +9183,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ……最高の舞台で、最高の結末。悪くないわね</t>
+          <t xml:space="preserve">あら、残念ね。でも次があるわ</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.seductive[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.normal.seductive[2]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[2]</t>
+          <t xml:space="preserve">postLose.normal.seductive[2]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9215,14 +9215,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見ててくれた？ これが私のすべてよ</t>
+          <t xml:space="preserve">悔しいけど…いい経験だったわ</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.normal.seductive[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">postMatchWin.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9247,14 +9247,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ、おたくの団体さん…少し気になってたの</t>
+          <t xml:space="preserve">ふふ、まずは一勝ね。次も魅せてあげるわ</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.normal.seductive[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.normal.seductive[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[2]</t>
+          <t xml:space="preserve">postMatchWin.normal.seductive[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9279,14 +9279,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">遊んであげるわ。……本気でね</t>
+          <t xml:space="preserve">勝てたわ。……でもまだ先がある</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.normal.seductive[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9296,12 +9296,12 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">postWin.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9311,14 +9311,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら…怖いのかしら。可哀想</t>
+          <t xml:space="preserve">いい経験だったわ。もっと魅せられるようになりたいわね</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.normal.seductive[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.normal.seductive[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9328,12 +9328,12 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[2]</t>
+          <t xml:space="preserve">postWin.normal.seductive[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9343,14 +9343,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃げるのね…。つまらないわ</t>
+          <t xml:space="preserve">まだまだこんなものじゃないわよ</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.normal.seductive[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.normal.seductive[1]</t>
+          <t xml:space="preserve">preFinal.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9375,14 +9375,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃったわね…悔しい</t>
+          <t xml:space="preserve">決勝…。最後の舞台、最高に魅せてあげるわ</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.normal.seductive[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.normal.seductive[2]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.normal.seductive[2]</t>
+          <t xml:space="preserve">preFinal.normal.seductive[2]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9407,14 +9407,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次はもっと綺麗に勝ってみせるわ</t>
+          <t xml:space="preserve">あと一つ。全てを懸けるわ</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.normal.seductive[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.normal.seductive[1]</t>
+          <t xml:space="preserve">preMatch.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9439,14 +9439,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、勝てたわね。素敵な対抗戦だったわ</t>
+          <t xml:space="preserve">次の相手…楽しみね</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.normal.seductive[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.normal.seductive[2]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9456,12 +9456,12 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.normal.seductive[2]</t>
+          <t xml:space="preserve">preMatch.normal.seductive[2]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9471,14 +9471,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝利の味は…格別ね</t>
+          <t xml:space="preserve">わたしの魅力、見せつけてあげる</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9488,12 +9488,12 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">summon.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9503,14 +9503,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、もう終わり？ 物足りなかったわ</t>
+          <t xml:space="preserve">出場が決まったわ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.normal.seductive[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.normal.seductive[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[2]</t>
+          <t xml:space="preserve">summon.normal.seductive[2]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9535,14 +9535,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うちの団体の底力、見せてあげたわよ</t>
+          <t xml:space="preserve">素敵な舞台ね。魅せてあげるわ</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.normal.seductive[3]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[3]</t>
+          <t xml:space="preserve">normal.seductive[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9567,44 +9567,524 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、うちの団体の魅力、わかっていただけたかしら</t>
+          <t xml:space="preserve">今日は負けるわけにはいかないの。覚悟してね</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふふ……最高の舞台で、最高の結末。悪くないわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="40" customHeight="1">
+      <c r="A290" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">見ててくれた？ これが私のすべてよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="40" customHeight="1">
+      <c r="A291" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.normal.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">うふふ、おたくの団体さん…少し気になってたの</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="40" customHeight="1">
+      <c r="A292" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.normal.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">遊んであげるわ。……本気でね</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="40" customHeight="1">
+      <c r="A293" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.normal.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら…怖いのかしら。可哀想</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="40" customHeight="1">
+      <c r="A294" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.normal.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">逃げるのね…。つまらないわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="40" customHeight="1">
+      <c r="A295" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.normal.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.normal.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">負けちゃったわね…悔しい</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="40" customHeight="1">
+      <c r="A296" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.normal.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.normal.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">次はもっと綺麗に勝ってみせるわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="40" customHeight="1">
+      <c r="A297" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.normal.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.normal.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふふ、勝てたわね。素敵な対抗戦だったわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="40" customHeight="1">
+      <c r="A298" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.normal.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.normal.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝利の味は…格別ね</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="40" customHeight="1">
+      <c r="A299" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.normal.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、もう終わり？ 物足りなかったわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="40" customHeight="1">
+      <c r="A300" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.normal.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">うちの団体の底力、見せてあげたわよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="40" customHeight="1">
+      <c r="A301" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.normal.seductive[3]</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.seductive[3]</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふふ、うちの団体の魅力、わかっていただけたかしら</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="40" customHeight="1">
+      <c r="A302" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">ENDING_LINES.fighter.normal.seductive[1]</t>
         </is>
       </c>
-      <c r="B289" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr" s="2">
+      <c r="B302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr" s="12">
+      <c r="D302" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighter.normal.seductive[1]</t>
         </is>
       </c>
-      <c r="E289" t="inlineStr" s="2">
+      <c r="E302" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
-      <c r="F289" t="inlineStr" s="3">
+      <c r="F302" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ここまで来れたのね…最高の気分だわ</t>
         </is>
       </c>
     </row>
+    <row r="303" ht="40" customHeight="1">
+      <c r="A303" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.normal.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">落ちこぼれを拾うなんて。…物好きね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="40" customHeight="1">
+      <c r="A304" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.normal.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">目をつけたのはそっち。…責任、取ってね</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H289"/>
+  <autoFilter ref="A1:H304"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/蠱惑×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×ノーマル.xlsx
@@ -386,7 +386,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.normal.seductive[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -401,7 +401,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.normal.seductive[1]</t>
+          <t xml:space="preserve">atk.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -418,7 +418,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.normal.seductive[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -433,7 +433,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.normal.seductive[2]</t>
+          <t xml:space="preserve">atk.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -450,7 +450,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.normal.seductive[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.seductive.normal[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -465,7 +465,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.normal.seductive[3]</t>
+          <t xml:space="preserve">atk.seductive.normal[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -482,7 +482,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.normal.seductive[4]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.seductive.normal[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -497,7 +497,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.normal.seductive[4]</t>
+          <t xml:space="preserve">atk.seductive.normal[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -514,7 +514,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.normal.seductive[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -529,7 +529,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.normal.seductive[1]</t>
+          <t xml:space="preserve">bigmove.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
@@ -546,7 +546,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.normal.seductive[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -561,7 +561,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.normal.seductive[2]</t>
+          <t xml:space="preserve">bigmove.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
@@ -578,7 +578,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.normal.seductive[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.seductive.normal[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -593,7 +593,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.normal.seductive[3]</t>
+          <t xml:space="preserve">bigmove.seductive.normal[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
@@ -610,7 +610,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.normal.seductive[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -625,7 +625,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.normal.seductive[1]</t>
+          <t xml:space="preserve">climax.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
@@ -642,7 +642,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.normal.seductive[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -657,7 +657,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.normal.seductive[2]</t>
+          <t xml:space="preserve">climax.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
@@ -674,7 +674,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -689,7 +689,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
@@ -706,7 +706,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.normal.seductive[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -721,7 +721,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[2]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
@@ -738,7 +738,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.normal.seductive[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.seductive.normal[3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -753,7 +753,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[3]</t>
+          <t xml:space="preserve">seductive.normal[3]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
@@ -770,7 +770,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.normal.seductive[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -785,7 +785,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.normal.seductive[1]</t>
+          <t xml:space="preserve">badWinner.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
@@ -802,7 +802,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.normal.seductive[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -817,7 +817,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.normal.seductive[1]</t>
+          <t xml:space="preserve">goodWinner.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
@@ -834,7 +834,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.normal.seductive[2]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -849,7 +849,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.normal.seductive[2]</t>
+          <t xml:space="preserve">goodWinner.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
@@ -866,7 +866,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -881,7 +881,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
@@ -898,7 +898,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.normal.seductive[2]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -913,7 +913,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[2]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -930,7 +930,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.normal.seductive[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -945,7 +945,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.seductive[1]</t>
+          <t xml:space="preserve">loser.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
@@ -962,7 +962,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.normal.seductive[2]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -977,7 +977,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.seductive[2]</t>
+          <t xml:space="preserve">loser.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
@@ -994,7 +994,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.normal.seductive[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.seductive[1]</t>
+          <t xml:space="preserve">winner.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -1026,7 +1026,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.normal.seductive[2]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.seductive[2]</t>
+          <t xml:space="preserve">winner.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
@@ -1058,7 +1058,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.normal.seductive[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.normal.seductive[1]</t>
+          <t xml:space="preserve">competition_won.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
@@ -1090,7 +1090,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.normal.seductive[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.normal.seductive[2]</t>
+          <t xml:space="preserve">competition_won.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
@@ -1122,7 +1122,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.normal.seductive[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.normal.seductive[1]</t>
+          <t xml:space="preserve">direct.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
@@ -1154,7 +1154,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.normal.seductive[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.normal.seductive[2]</t>
+          <t xml:space="preserve">direct.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
@@ -1186,7 +1186,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.normal.seductive[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.normal.seductive[1]</t>
+          <t xml:space="preserve">fa_signing.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
@@ -1218,7 +1218,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.normal.seductive[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.normal.seductive[2]</t>
+          <t xml:space="preserve">fa_signing.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
@@ -1250,7 +1250,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.normal.seductive.hit[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.seductive.normal.hit[1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive.hit[1]</t>
+          <t xml:space="preserve">seductive.normal.hit[1]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
@@ -1282,7 +1282,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.normal.seductive.hit[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.seductive.normal.hit[2]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive.hit[2]</t>
+          <t xml:space="preserve">seductive.normal.hit[2]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -1314,7 +1314,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.normal.seductive.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.seductive.normal.win[1]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive.win[1]</t>
+          <t xml:space="preserve">seductive.normal.win[1]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -1346,7 +1346,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.normal.seductive.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.seductive.normal.win[2]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive.win[2]</t>
+          <t xml:space="preserve">seductive.normal.win[2]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
@@ -1378,7 +1378,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
@@ -1410,7 +1410,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.normal.seductive[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[2]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
@@ -1442,7 +1442,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.normal.seductive[3]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.seductive.normal[3]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[3]</t>
+          <t xml:space="preserve">seductive.normal[3]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
@@ -1474,7 +1474,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1506,7 +1506,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.normal.seductive[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[2]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1538,7 +1538,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.normal.seductive[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.seductive.normal[3]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[3]</t>
+          <t xml:space="preserve">seductive.normal[3]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
@@ -1570,7 +1570,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
@@ -1602,7 +1602,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.normal.seductive[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[2]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1634,7 +1634,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.normal.seductive[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.seductive.normal[3]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[3]</t>
+          <t xml:space="preserve">seductive.normal[3]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1666,7 +1666,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1698,7 +1698,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.normal.seductive[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[2]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1730,7 +1730,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.normal.seductive[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.seductive.normal[3]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[3]</t>
+          <t xml:space="preserve">seductive.normal[3]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1762,7 +1762,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1794,7 +1794,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.normal.seductive[2]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[2]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1826,7 +1826,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1858,7 +1858,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.normal.seductive[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[2]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1890,7 +1890,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.normal.seductive[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.seductive[1]</t>
+          <t xml:space="preserve">loser.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1922,7 +1922,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.normal.seductive[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.seductive[1]</t>
+          <t xml:space="preserve">winner.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1954,7 +1954,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.normal.seductive[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.seductive[1]</t>
+          <t xml:space="preserve">winner.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1986,7 +1986,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.normal.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal.seductive[1]</t>
+          <t xml:space="preserve">attacker.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -2018,7 +2018,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.normal.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal.seductive[1]</t>
+          <t xml:space="preserve">defender.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -2050,7 +2050,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.normal.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal.seductive[1]</t>
+          <t xml:space="preserve">attacker.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2082,7 +2082,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.normal.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal.seductive[1]</t>
+          <t xml:space="preserve">defender.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2114,7 +2114,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.normal.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal.seductive[1]</t>
+          <t xml:space="preserve">attacker.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2146,7 +2146,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.normal.seductive[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal.seductive[2]</t>
+          <t xml:space="preserve">attacker.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2178,7 +2178,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.normal.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal.seductive[1]</t>
+          <t xml:space="preserve">defender.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2210,7 +2210,7 @@
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.normal.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.normal.seductive[1]</t>
+          <t xml:space="preserve">fateAttacker.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2242,7 +2242,7 @@
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.normal.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.normal.seductive[1]</t>
+          <t xml:space="preserve">fateDefender.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
@@ -2274,7 +2274,7 @@
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.normal.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.normal.seductive[1]</t>
+          <t xml:space="preserve">loserLines.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -2306,7 +2306,7 @@
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.normal.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.normal.seductive[1]</t>
+          <t xml:space="preserve">winnerLines.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="2">
@@ -2338,7 +2338,7 @@
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.normal.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.normal.seductive[1]</t>
+          <t xml:space="preserve">fateLoser.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr" s="2">
@@ -2370,7 +2370,7 @@
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.normal.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.normal.seductive[1]</t>
+          <t xml:space="preserve">fateWinner.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr" s="2">
@@ -2402,7 +2402,7 @@
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.normal.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.seductive[1]</t>
+          <t xml:space="preserve">loser.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr" s="2">
@@ -2434,7 +2434,7 @@
     <row r="66" ht="40" customHeight="1">
       <c r="A66" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.normal.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="D66" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.seductive[1]</t>
+          <t xml:space="preserve">winner.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr" s="2">
@@ -2466,7 +2466,7 @@
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.normal.seductive[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D67" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.normal.seductive[1]</t>
+          <t xml:space="preserve">loserLines.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr" s="2">
@@ -2498,7 +2498,7 @@
     <row r="68" ht="40" customHeight="1">
       <c r="A68" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.normal.seductive[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="D68" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.normal.seductive[1]</t>
+          <t xml:space="preserve">winnerLines.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr" s="2">
@@ -2530,7 +2530,7 @@
     <row r="69" ht="40" customHeight="1">
       <c r="A69" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.normal.seductive[1]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="D69" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.normal.seductive[1]</t>
+          <t xml:space="preserve">awakening.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr" s="2">
@@ -3330,7 +3330,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.normal.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.normal.seductive[1]</t>
+          <t xml:space="preserve">accepted.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3362,7 +3362,7 @@
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.normal.seductive[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.normal.seductive[2]</t>
+          <t xml:space="preserve">accepted.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3394,7 +3394,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.normal.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.normal.seductive[1]</t>
+          <t xml:space="preserve">defended.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3426,7 +3426,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.normal.seductive[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.normal.seductive[2]</t>
+          <t xml:space="preserve">defended.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3458,7 +3458,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.normal.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.normal.seductive[1]</t>
+          <t xml:space="preserve">defense_failed.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3490,7 +3490,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.normal.seductive[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.normal.seductive[2]</t>
+          <t xml:space="preserve">defense_failed.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3522,7 +3522,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.normal.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.normal.seductive[1]</t>
+          <t xml:space="preserve">default.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3554,7 +3554,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.normal.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.normal.seductive[1]</t>
+          <t xml:space="preserve">former_champ.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3586,7 +3586,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.normal.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.normal.seductive[1]</t>
+          <t xml:space="preserve">heel.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3618,7 +3618,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.normal.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.normal.seductive[1]</t>
+          <t xml:space="preserve">high_trust.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3650,7 +3650,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.normal.seductive[1]</t>
+          <t xml:space="preserve">accept_former_champ.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3682,7 +3682,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.normal.seductive[1]</t>
+          <t xml:space="preserve">accept_heel.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3714,7 +3714,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.normal.seductive[1]</t>
+          <t xml:space="preserve">accept_no_title.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3746,7 +3746,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.normal.seductive[1]</t>
+          <t xml:space="preserve">accept_terminal.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3778,7 +3778,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.normal.seductive[1]</t>
+          <t xml:space="preserve">accept_winless.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3810,7 +3810,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.normal.seductive[1]</t>
+          <t xml:space="preserve">refuse_champ.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3842,7 +3842,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.normal.seductive[1]</t>
+          <t xml:space="preserve">refuse_distrust.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3874,7 +3874,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.normal.seductive[1]</t>
+          <t xml:space="preserve">refuse_fighting.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3906,7 +3906,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.normal.seductive[1]</t>
+          <t xml:space="preserve">refuse_heel.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3938,7 +3938,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.normal.seductive[1]</t>
+          <t xml:space="preserve">A1_champion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3970,7 +3970,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.normal.seductive[1]</t>
+          <t xml:space="preserve">A2_uncrowned.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -4002,7 +4002,7 @@
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.normal.seductive[1]</t>
+          <t xml:space="preserve">A3_heel.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4034,7 +4034,7 @@
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.normal.seductive[1]</t>
+          <t xml:space="preserve">A4_veteran.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4066,7 +4066,7 @@
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.normal.seductive[1]</t>
+          <t xml:space="preserve">B1_young.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4098,7 +4098,7 @@
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.normal.seductive[1]</t>
+          <t xml:space="preserve">B2_prime.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4130,7 +4130,7 @@
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.normal.seductive[1]</t>
+          <t xml:space="preserve">B3_older.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4162,7 +4162,7 @@
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.normal.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.normal.seductive[1]</t>
+          <t xml:space="preserve">B4_champion_injury.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4194,7 +4194,7 @@
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4226,7 +4226,7 @@
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.normal.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.normal.seductive[1]</t>
+          <t xml:space="preserve">raise_accept.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4258,7 +4258,7 @@
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.normal.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.normal.seductive[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4290,7 +4290,7 @@
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.normal.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.normal.seductive[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4322,7 +4322,7 @@
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.normal.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.normal.seductive[1]</t>
+          <t xml:space="preserve">raise_open.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4354,7 +4354,7 @@
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.normal.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.normal.seductive[1]</t>
+          <t xml:space="preserve">raise_refuse.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4386,7 +4386,7 @@
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.normal.seductive[1]</t>
+          <t xml:space="preserve">sudden_departure.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4418,7 +4418,7 @@
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal.seductive[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.normal.seductive[2]</t>
+          <t xml:space="preserve">sudden_departure.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4450,7 +4450,7 @@
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.normal.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.normal.seductive[1]</t>
+          <t xml:space="preserve">transfer_listen.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4482,7 +4482,7 @@
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.normal.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.normal.seductive[1]</t>
+          <t xml:space="preserve">transfer_open.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4514,7 +4514,7 @@
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.normal.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.normal.seductive[1]</t>
+          <t xml:space="preserve">transfer_release.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4546,7 +4546,7 @@
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.normal.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.normal.seductive[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4578,7 +4578,7 @@
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.normal.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.normal.seductive[1]</t>
+          <t xml:space="preserve">transfer_retain_success.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4610,7 +4610,7 @@
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.normal.seductive[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.normal.seductive[1]</t>
+          <t xml:space="preserve">blocked.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4643,7 +4643,7 @@
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.normal.seductive[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.normal.seductive[1]</t>
+          <t xml:space="preserve">fail.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4676,7 +4676,7 @@
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.normal.seductive[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.normal.seductive[1]</t>
+          <t xml:space="preserve">start.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4709,7 +4709,7 @@
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.normal.seductive[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.normal.seductive[1]</t>
+          <t xml:space="preserve">success.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4742,7 +4742,7 @@
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4774,7 +4774,7 @@
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4806,7 +4806,7 @@
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.normal.seductive[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.normal.seductive[1]</t>
+          <t xml:space="preserve">cap_reached.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4838,7 +4838,7 @@
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.normal.seductive[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.normal.seductive[1]</t>
+          <t xml:space="preserve">ovr_elite.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4870,7 +4870,7 @@
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.normal.seductive[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.normal.seductive[1]</t>
+          <t xml:space="preserve">ovr_growth.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4902,7 +4902,7 @@
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.normal.seductive[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.normal.seductive[1]</t>
+          <t xml:space="preserve">ovr_legend.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4934,7 +4934,7 @@
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.normal.seductive[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.normal.seductive[1]</t>
+          <t xml:space="preserve">pop_growth.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4966,7 +4966,7 @@
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.normal.seductive[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.normal.seductive[1]</t>
+          <t xml:space="preserve">pop_star.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4998,7 +4998,7 @@
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -5030,7 +5030,7 @@
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5062,7 +5062,7 @@
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5094,7 +5094,7 @@
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.normal.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.normal.seductive[1]</t>
+          <t xml:space="preserve">defeat.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5126,7 +5126,7 @@
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.normal.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.normal.seductive[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5158,7 +5158,7 @@
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.normal.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.normal.seductive[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5190,7 +5190,7 @@
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.normal.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.normal.seductive[1]</t>
+          <t xml:space="preserve">penalty_end.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5222,7 +5222,7 @@
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.normal.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.normal.seductive[1]</t>
+          <t xml:space="preserve">bestMatch.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5254,7 +5254,7 @@
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.normal.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.seductive[1]</t>
+          <t xml:space="preserve">champion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5286,7 +5286,7 @@
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.normal.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.normal.seductive[1]</t>
+          <t xml:space="preserve">hallOfFame.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5318,7 +5318,7 @@
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.normal.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.normal.seductive[1]</t>
+          <t xml:space="preserve">mediaAward.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5350,7 +5350,7 @@
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.normal.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.normal.seductive[1]</t>
+          <t xml:space="preserve">mvp.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5382,7 +5382,7 @@
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.normal.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.normal.seductive[1]</t>
+          <t xml:space="preserve">rookie.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5414,7 +5414,7 @@
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5446,7 +5446,7 @@
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.seductive[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[2]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5478,7 +5478,7 @@
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.seductive[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.normal[3]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[3]</t>
+          <t xml:space="preserve">seductive.normal[3]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5510,7 +5510,7 @@
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5542,7 +5542,7 @@
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.seductive[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[2]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5574,7 +5574,7 @@
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.seductive[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.normal[3]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[3]</t>
+          <t xml:space="preserve">seductive.normal[3]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5606,7 +5606,7 @@
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.normal.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.normal.seductive[1]</t>
+          <t xml:space="preserve">N1.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5638,7 +5638,7 @@
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.normal.seductive[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.normal.seductive[2]</t>
+          <t xml:space="preserve">N1.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5670,7 +5670,7 @@
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.normal.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.normal.seductive[1]</t>
+          <t xml:space="preserve">N2.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5702,7 +5702,7 @@
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.normal.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.normal.seductive[1]</t>
+          <t xml:space="preserve">N3.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5734,7 +5734,7 @@
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.normal.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.normal.seductive[1]</t>
+          <t xml:space="preserve">N4.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5766,7 +5766,7 @@
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.normal.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.normal.seductive[1]</t>
+          <t xml:space="preserve">N5_low.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5798,7 +5798,7 @@
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.normal.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.normal.seductive[1]</t>
+          <t xml:space="preserve">N5_warning.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5830,7 +5830,7 @@
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.normal.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.normal.seductive[1]</t>
+          <t xml:space="preserve">bonus_insult.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5862,7 +5862,7 @@
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.normal.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.normal.seductive[1]</t>
+          <t xml:space="preserve">bonus.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5894,7 +5894,7 @@
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.normal.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.normal.seductive[1]</t>
+          <t xml:space="preserve">camp.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5926,7 +5926,7 @@
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.normal.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.normal.seductive[1]</t>
+          <t xml:space="preserve">encourage_high_trust.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5958,7 +5958,7 @@
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.normal.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.normal.seductive[1]</t>
+          <t xml:space="preserve">encourage.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5990,7 +5990,7 @@
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.normal.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.normal.seductive[1]</t>
+          <t xml:space="preserve">media.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -6022,7 +6022,7 @@
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.normal.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.normal.seductive[1]</t>
+          <t xml:space="preserve">party.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6054,7 +6054,7 @@
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.normal.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.normal.seductive[1]</t>
+          <t xml:space="preserve">refresh_leave.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6086,7 +6086,7 @@
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.normal.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.normal.seductive[1]</t>
+          <t xml:space="preserve">special_treatment.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6118,7 +6118,7 @@
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.normal.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.normal.seductive[1]</t>
+          <t xml:space="preserve">trainer.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6150,7 +6150,7 @@
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.normal.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.normal.seductive[1]</t>
+          <t xml:space="preserve">E1.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6182,7 +6182,7 @@
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.normal.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E4.normal.seductive[1]</t>
+          <t xml:space="preserve">E4.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6214,7 +6214,7 @@
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.normal.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.normal.seductive[1]</t>
+          <t xml:space="preserve">E6.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6246,7 +6246,7 @@
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.normal.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.normal.seductive[1]</t>
+          <t xml:space="preserve">S_boycott.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6278,7 +6278,7 @@
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.normal.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.normal.seductive[1]</t>
+          <t xml:space="preserve">S_grumble.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6310,7 +6310,7 @@
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.normal.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.normal.seductive[1]</t>
+          <t xml:space="preserve">S_sns.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6342,7 +6342,7 @@
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.normal.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.normal.seductive[1]</t>
+          <t xml:space="preserve">S1.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6374,7 +6374,7 @@
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.normal.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.normal.seductive[1]</t>
+          <t xml:space="preserve">S2.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6406,7 +6406,7 @@
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.normal.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.normal.seductive[1]</t>
+          <t xml:space="preserve">S3.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6438,7 +6438,7 @@
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.normal.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.normal.seductive[1]</t>
+          <t xml:space="preserve">S4_direct.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6470,7 +6470,7 @@
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.normal.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.normal.seductive[1]</t>
+          <t xml:space="preserve">S4_silent.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6502,7 +6502,7 @@
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.normal.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.normal.seductive[1]</t>
+          <t xml:space="preserve">S5.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6534,7 +6534,7 @@
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.normal.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.normal.seductive[1]</t>
+          <t xml:space="preserve">S6.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6566,7 +6566,7 @@
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.normal.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.normal.seductive[1]</t>
+          <t xml:space="preserve">B1.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6598,7 +6598,7 @@
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.normal.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.normal.seductive[1]</t>
+          <t xml:space="preserve">B2_fighter1.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6630,7 +6630,7 @@
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.normal.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.normal.seductive[1]</t>
+          <t xml:space="preserve">B2_fighter2.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6662,7 +6662,7 @@
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.normal.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.normal.seductive[1]</t>
+          <t xml:space="preserve">B4_brand.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6694,7 +6694,7 @@
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.normal.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.normal.seductive[1]</t>
+          <t xml:space="preserve">B4_cm.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6726,7 +6726,7 @@
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.normal.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.normal.seductive[1]</t>
+          <t xml:space="preserve">B4_fan.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6758,7 +6758,7 @@
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.normal.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.normal.seductive[1]</t>
+          <t xml:space="preserve">B4_fashion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6790,7 +6790,7 @@
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.normal.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.normal.seductive[1]</t>
+          <t xml:space="preserve">B4_gravure.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6822,7 +6822,7 @@
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.normal.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.normal.seductive[1]</t>
+          <t xml:space="preserve">B4_variety.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6854,7 +6854,7 @@
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.normal.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.normal.seductive[1]</t>
+          <t xml:space="preserve">B4.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6886,7 +6886,7 @@
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6918,7 +6918,7 @@
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6950,7 +6950,7 @@
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.seductive[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[2]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6982,7 +6982,7 @@
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -7014,7 +7014,7 @@
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7046,7 +7046,7 @@
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7078,7 +7078,7 @@
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.normal.seductive[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[2]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7110,7 +7110,7 @@
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.normal.seductive[1]</t>
+          <t xml:space="preserve">draftInterest.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7142,7 +7142,7 @@
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.normal.seductive[1]</t>
+          <t xml:space="preserve">draftJoin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7174,7 +7174,7 @@
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.normal.seductive[2]</t>
+          <t xml:space="preserve">draftJoin.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7206,7 +7206,7 @@
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.normal.seductive[1]</t>
+          <t xml:space="preserve">faGreeting.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7238,7 +7238,7 @@
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.normal.seductive[1]</t>
+          <t xml:space="preserve">faSigning.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7270,7 +7270,7 @@
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.normal.seductive[1]</t>
+          <t xml:space="preserve">faWelcome.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7302,7 +7302,7 @@
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.normal.seductive[1]</t>
+          <t xml:space="preserve">injury.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7334,7 +7334,7 @@
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.normal.seductive[2]</t>
+          <t xml:space="preserve">injury.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7366,7 +7366,7 @@
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.normal.seductive[1]</t>
+          <t xml:space="preserve">release.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7398,7 +7398,7 @@
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.normal.seductive[2]</t>
+          <t xml:space="preserve">release.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7430,7 +7430,7 @@
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.normal.seductive[1]</t>
+          <t xml:space="preserve">rentalGreeting.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7462,7 +7462,7 @@
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.normal.seductive[1]</t>
+          <t xml:space="preserve">scoutGreeting.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7494,7 +7494,7 @@
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.normal.seductive[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7526,7 +7526,7 @@
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.normal.seductive[1]</t>
+          <t xml:space="preserve">titleDefense.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7558,7 +7558,7 @@
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.normal.seductive[1]</t>
+          <t xml:space="preserve">titleLoss.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7590,7 +7590,7 @@
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.normal.seductive[1]</t>
+          <t xml:space="preserve">titleWin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7622,7 +7622,7 @@
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7654,7 +7654,7 @@
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.seductive[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[2]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7686,7 +7686,7 @@
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7718,7 +7718,7 @@
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7750,7 +7750,7 @@
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7782,7 +7782,7 @@
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7814,7 +7814,7 @@
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -8198,7 +8198,7 @@
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.normal.seductive[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8230,7 +8230,7 @@
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.normal.seductive[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8262,7 +8262,7 @@
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.normal.seductive[1]</t>
+          <t xml:space="preserve">GL-01.loss.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8294,7 +8294,7 @@
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.normal.seductive[1]</t>
+          <t xml:space="preserve">GL-01.win.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8326,7 +8326,7 @@
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.normal.seductive[1]</t>
+          <t xml:space="preserve">GL-02.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8358,7 +8358,7 @@
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.normal.seductive[1]</t>
+          <t xml:space="preserve">GL-03.down.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8390,7 +8390,7 @@
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.normal.seductive[1]</t>
+          <t xml:space="preserve">GL-03.up.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8422,7 +8422,7 @@
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8437,7 +8437,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.normal.seductive[1]</t>
+          <t xml:space="preserve">GL-04.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8454,7 +8454,7 @@
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8469,7 +8469,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.normal.seductive[1]</t>
+          <t xml:space="preserve">GL-05.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8486,7 +8486,7 @@
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.normal.seductive[1]</t>
+          <t xml:space="preserve">GL-06.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8518,7 +8518,7 @@
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.normal.seductive[1]</t>
+          <t xml:space="preserve">GL-07.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8550,7 +8550,7 @@
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8565,7 +8565,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.normal.seductive[1]</t>
+          <t xml:space="preserve">GL-08.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8582,7 +8582,7 @@
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.normal.seductive[1]</t>
+          <t xml:space="preserve">GL-09.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8614,7 +8614,7 @@
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.normal.seductive[1]</t>
+          <t xml:space="preserve">GL-10.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8646,7 +8646,7 @@
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.normal.seductive[1]</t>
+          <t xml:space="preserve">GL-11.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8678,7 +8678,7 @@
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8710,7 +8710,7 @@
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8725,7 +8725,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.seductive[1]</t>
+          <t xml:space="preserve">preFinal.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8742,7 +8742,7 @@
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.seductive[2]</t>
+          <t xml:space="preserve">preFinal.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8774,7 +8774,7 @@
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.seductive[1]</t>
+          <t xml:space="preserve">preMatch.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8806,7 +8806,7 @@
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.seductive[2]</t>
+          <t xml:space="preserve">preMatch.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8838,7 +8838,7 @@
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.normal.seductive[1]</t>
+          <t xml:space="preserve">survivor.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8870,7 +8870,7 @@
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8885,7 +8885,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.normal.seductive[2]</t>
+          <t xml:space="preserve">survivor.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8902,7 +8902,7 @@
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.seductive[1]</t>
+          <t xml:space="preserve">champion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8934,7 +8934,7 @@
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.seductive[2]</t>
+          <t xml:space="preserve">champion.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8966,7 +8966,7 @@
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.normal.seductive[1]</t>
+          <t xml:space="preserve">defiant.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8998,7 +8998,7 @@
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.normal.seductive[2]</t>
+          <t xml:space="preserve">defiant.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9030,7 +9030,7 @@
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9045,7 +9045,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.normal.seductive[1]</t>
+          <t xml:space="preserve">gauntlet.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9062,7 +9062,7 @@
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.normal.seductive[2]</t>
+          <t xml:space="preserve">gauntlet.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9094,7 +9094,7 @@
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.normal.seductive[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.seductive[1]</t>
+          <t xml:space="preserve">champion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9126,7 +9126,7 @@
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.normal.seductive[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.seductive[2]</t>
+          <t xml:space="preserve">champion.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9158,7 +9158,7 @@
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.normal.seductive[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9173,7 +9173,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.normal.seductive[1]</t>
+          <t xml:space="preserve">postLose.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9190,7 +9190,7 @@
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.normal.seductive[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.normal.seductive[2]</t>
+          <t xml:space="preserve">postLose.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9222,7 +9222,7 @@
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.normal.seductive[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.normal.seductive[1]</t>
+          <t xml:space="preserve">postMatchWin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9254,7 +9254,7 @@
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.normal.seductive[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.normal.seductive[2]</t>
+          <t xml:space="preserve">postMatchWin.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9286,7 +9286,7 @@
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.normal.seductive[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.normal.seductive[1]</t>
+          <t xml:space="preserve">postWin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9318,7 +9318,7 @@
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.normal.seductive[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.normal.seductive[2]</t>
+          <t xml:space="preserve">postWin.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9350,7 +9350,7 @@
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.normal.seductive[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9365,7 +9365,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.seductive[1]</t>
+          <t xml:space="preserve">preFinal.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9382,7 +9382,7 @@
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.normal.seductive[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.seductive[2]</t>
+          <t xml:space="preserve">preFinal.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9414,7 +9414,7 @@
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.normal.seductive[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.seductive[1]</t>
+          <t xml:space="preserve">preMatch.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9446,7 +9446,7 @@
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.normal.seductive[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.seductive[2]</t>
+          <t xml:space="preserve">preMatch.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9478,7 +9478,7 @@
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.normal.seductive[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9493,7 +9493,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.normal.seductive[1]</t>
+          <t xml:space="preserve">summon.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9510,7 +9510,7 @@
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.normal.seductive[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.normal.seductive[2]</t>
+          <t xml:space="preserve">summon.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9542,7 +9542,7 @@
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9574,7 +9574,7 @@
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9606,7 +9606,7 @@
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.seductive[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9621,7 +9621,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[2]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9638,7 +9638,7 @@
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.normal.seductive[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9670,7 +9670,7 @@
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.normal.seductive[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[2]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9702,7 +9702,7 @@
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.normal.seductive[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9734,7 +9734,7 @@
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.normal.seductive[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[2]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9766,7 +9766,7 @@
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.normal.seductive[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.normal.seductive[1]</t>
+          <t xml:space="preserve">result_lose.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9798,7 +9798,7 @@
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.normal.seductive[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.normal.seductive[2]</t>
+          <t xml:space="preserve">result_lose.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9830,7 +9830,7 @@
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.normal.seductive[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.normal.seductive[1]</t>
+          <t xml:space="preserve">result_win.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9862,7 +9862,7 @@
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.normal.seductive[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.normal.seductive[2]</t>
+          <t xml:space="preserve">result_win.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9894,7 +9894,7 @@
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9926,7 +9926,7 @@
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.normal.seductive[2]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[2]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9958,7 +9958,7 @@
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.normal.seductive[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.normal[3]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9973,7 +9973,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[3]</t>
+          <t xml:space="preserve">seductive.normal[3]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9990,7 +9990,7 @@
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.normal.seductive[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.normal.seductive[1]</t>
+          <t xml:space="preserve">fighter.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -10022,7 +10022,7 @@
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10054,7 +10054,7 @@
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.normal.seductive[1]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">

--- a/セリフ編集/キャラタイプ別/蠱惑×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×ノーマル.xlsx
@@ -193,7 +193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -205,7 +205,7 @@
     <row r="1">
       <c r="A1" t="inlineStr" s="11">
         <is>
-          <t xml:space="preserve">このタイプ(蠱惑×ノーマル)に該当するキャラクター: 4名</t>
+          <t xml:space="preserve">このタイプ(蠱惑×ノーマル)に該当するキャラクター: 2名</t>
         </is>
       </c>
     </row>
@@ -273,50 +273,6 @@
       <c r="D5" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">ライバル体質、負けず嫌い</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">長谷川レオナ</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Allround</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Neutral</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">人望、引き出し上手</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">山本理香</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Striker</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Neutral</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">頑丈さ</t>
         </is>
       </c>
     </row>
@@ -328,7 +284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H304"/>
+  <dimension ref="A1:H306"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -763,7 +719,7 @@
       </c>
       <c r="F13" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はぁ…少し本気になったわ…</t>
+          <t xml:space="preserve">はぁ…少し本気を見せてあげる…</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1039,7 @@
       </c>
       <c r="F23" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私のために争ってくれたの？ …ちょっと嬉しいかも♡</t>
+          <t xml:space="preserve">私のために争ってくれたの？ …ふふ、悪くない気分よ♡</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1711,7 @@
       </c>
       <c r="F44" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここからはわたしの番ね</t>
+          <t xml:space="preserve">ここからは私の番ね</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1743,7 @@
       </c>
       <c r="F45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{partner}…ごめんなさい。わたしが決めきれてたら…</t>
+          <t xml:space="preserve">{partner}…ごめんなさい。私が決めきれてたら…</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2671,7 @@
       </c>
       <c r="F74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{org}のあいつが気に障るのよね・・・対戦、セッティングしてくれる?</t>
+          <t xml:space="preserve">{org}のあの子が気に障るのよね……対戦、セッティングしてくれる？</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2895,7 @@
       </c>
       <c r="F81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい顔してる? やっぱり勝った後だからかしらね。ふふ♪</t>
+          <t xml:space="preserve">いい顔してる？ やっぱり勝った後だからかしらね。ふふ♪</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2927,7 @@
       </c>
       <c r="F82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、私を選んだの? 光栄だわ。</t>
+          <t xml:space="preserve">あら、私を選んだの？ 光栄だわ。</t>
         </is>
       </c>
     </row>
@@ -3035,7 +2991,7 @@
       </c>
       <c r="F84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そんなに私が欲しいの? …来なさい。</t>
+          <t xml:space="preserve">そんなに私が欲しいの？ …来なさい。</t>
         </is>
       </c>
     </row>
@@ -3099,7 +3055,7 @@
       </c>
       <c r="F86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">続きは、また今度。ね?</t>
+          <t xml:space="preserve">続きは、また今度。ね？</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3215,7 @@
       </c>
       <c r="F91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ね、届かなかったでしょう?</t>
+          <t xml:space="preserve">ね、届かなかったでしょう？</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3247,7 @@
       </c>
       <c r="F92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、いい夢は見られた?</t>
+          <t xml:space="preserve">ふふ、いい夢は見られた？</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4207,7 @@
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがと、社長♡ もっと頑張っちゃうからね。</t>
+          <t xml:space="preserve">ありがと、社長♡ もっと魅せてあげるわね。</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5178,7 @@
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.seductive.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5237,7 +5193,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.seductive.normal[1]</t>
+          <t xml:space="preserve">autumnWarChampion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5247,14 +5203,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高に痺れたわ。…また味わいたい、あの感覚</t>
+          <t xml:space="preserve">団体の名を背負うなら、このくらい華やかに勝たなきゃ。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.seductive.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5269,7 +5225,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.normal[1]</t>
+          <t xml:space="preserve">bestMatch.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5279,14 +5235,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この輝き、よく似合うでしょう？ 欲しいなら…奪いに来なさい</t>
+          <t xml:space="preserve">最高に痺れたわ。…また味わいたい、あの感覚</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.seductive.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5301,7 +5257,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.seductive.normal[1]</t>
+          <t xml:space="preserve">champion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5311,14 +5267,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">素敵な花道を用意してくれるのね。…ありがとう。最高の舞台だったわ</t>
+          <t xml:space="preserve">この輝き、よく似合うでしょう？ 欲しいなら…奪いに来なさい</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.seductive.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5333,7 +5289,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.seductive.normal[1]</t>
+          <t xml:space="preserve">hallOfFame.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5343,14 +5299,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、私の魅力が伝わったかしら</t>
+          <t xml:space="preserve">素敵な花道を用意してくれるのね。…ありがとう。最高の舞台だったわ</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.seductive.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5365,7 +5321,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.seductive.normal[1]</t>
+          <t xml:space="preserve">mediaAward.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5375,14 +5331,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一年間ずっと見ていてくれたでしょう？ …ちゃんと応えたわ</t>
+          <t xml:space="preserve">ふふ、私の魅力が伝わったかしら</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.seductive.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5397,7 +5353,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.seductive.normal[1]</t>
+          <t xml:space="preserve">mvp.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5407,14 +5363,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">覚えておいて。この名前、来年はもっと大きなところで呼ばれるから</t>
+          <t xml:space="preserve">一年間ずっと見ていてくれたでしょう？ …ちゃんと応えたわ</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5424,12 +5380,12 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">rookie.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5439,14 +5395,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふっ、いよいよドームね</t>
+          <t xml:space="preserve">覚えておいて。この名前、来年はもっと大きなところで呼ばれるから</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.normal[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5456,12 +5412,12 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[2]</t>
+          <t xml:space="preserve">springTagChampion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5471,14 +5427,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この大舞台で…見せたいものがあるの</t>
+          <t xml:space="preserve">ふたりで掴んだ春の主役の座、悪くない気分でしょう？</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.normal[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5493,7 +5449,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[3]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5503,14 +5459,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドームのお客様を…虜にしてあげる</t>
+          <t xml:space="preserve">ふふっ、いよいよドームね</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5520,12 +5476,12 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5535,14 +5491,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員のお客様…今夜の私に、酔いしれてくれたのね</t>
+          <t xml:space="preserve">この大舞台で…見せたいものがあるの</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.normal[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.normal[3]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5552,12 +5508,12 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[2]</t>
+          <t xml:space="preserve">seductive.normal[3]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5567,14 +5523,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ…この達成感、格別ね</t>
+          <t xml:space="preserve">ドームのお客様を…虜にしてあげる</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.normal[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5589,7 +5545,7 @@
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[3]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5599,14 +5555,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">忘れられない夜になったわ</t>
+          <t xml:space="preserve">満員のお客様…今夜の私に、酔いしれてくれたのね</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.normal[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5616,29 +5572,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近、体が素直に動いてくれるの。嬉しいわ</t>
+          <t xml:space="preserve">うふふ…この達成感、格別ね</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.normal[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.normal[3]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5648,29 +5604,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.seductive.normal[2]</t>
+          <t xml:space="preserve">seductive.normal[3]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習が楽しくなってきた気がする</t>
+          <t xml:space="preserve">忘れられない夜になったわ</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.seductive.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5685,7 +5641,7 @@
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.seductive.normal[1]</t>
+          <t xml:space="preserve">N1.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5695,14 +5651,14 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい仲間に恵まれたわ。心強いの</t>
+          <t xml:space="preserve">最近、体が素直に動いてくれるの。嬉しいわ</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.seductive.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5717,7 +5673,7 @@
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.seductive.normal[1]</t>
+          <t xml:space="preserve">N1.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5727,14 +5683,14 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少し疲れただけよ。心配しないで</t>
+          <t xml:space="preserve">練習が楽しくなってきた気がする</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.seductive.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5749,7 +5705,7 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.seductive.normal[1]</t>
+          <t xml:space="preserve">N2.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5759,14 +5715,14 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなに応援してもらえるなんて…嬉しいわ</t>
+          <t xml:space="preserve">いい仲間に恵まれたわ。心強いの</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.seductive.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5781,7 +5737,7 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.seductive.normal[1]</t>
+          <t xml:space="preserve">N3.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5791,14 +5747,14 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もういいわ。分かったから</t>
+          <t xml:space="preserve">少し疲れただけよ。心配しないで</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.seductive.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5813,7 +5769,7 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.seductive.normal[1]</t>
+          <t xml:space="preserve">N4.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5823,14 +5779,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい、ちょっと考え事してて</t>
+          <t xml:space="preserve">こんなに応援してもらえるなんて…嬉しいわ</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.seductive.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5840,29 +5796,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.seductive.normal[1]</t>
+          <t xml:space="preserve">N5_low.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら……ずいぶん安く見られたものね</t>
+          <t xml:space="preserve">…もういいわ。分かったから</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.seductive.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5872,29 +5828,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.seductive.normal[1]</t>
+          <t xml:space="preserve">N5_warning.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、嬉しい。ありがとう</t>
+          <t xml:space="preserve">…ごめんなさい、ちょっと考え事してて</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.seductive.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5909,7 +5865,7 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.seductive.normal[1]</t>
+          <t xml:space="preserve">bonus_insult.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5919,14 +5875,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合宿ね。しっかり鍛えるわ</t>
+          <t xml:space="preserve">あら……ずいぶん安く見られたものね</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.seductive.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5941,7 +5897,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.seductive.normal[1]</t>
+          <t xml:space="preserve">bonus.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5951,14 +5907,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと見てくれてたのね…嬉しい。頑張るわ</t>
+          <t xml:space="preserve">あら、嬉しい。ありがとう</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.seductive.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5973,7 +5929,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.seductive.normal[1]</t>
+          <t xml:space="preserve">camp.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5983,14 +5939,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。もう少し、頑張ってみるわ</t>
+          <t xml:space="preserve">合宿ね。しっかり鍛えるわ</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.seductive.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -6005,7 +5961,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.seductive.normal[1]</t>
+          <t xml:space="preserve">encourage_high_trust.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -6015,14 +5971,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">メディア出演…？ 楽しみだわ</t>
+          <t xml:space="preserve">ずっと見てくれてたのね…嬉しい。頑張るわ</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.seductive.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6037,7 +5993,7 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.seductive.normal[1]</t>
+          <t xml:space="preserve">encourage.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6047,14 +6003,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しかったわ。こういう時間もいいわね</t>
+          <t xml:space="preserve">…ありがとう。もう少し、頑張ってみるわ</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.seductive.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6069,7 +6025,7 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.seductive.normal[1]</t>
+          <t xml:space="preserve">media.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6079,14 +6035,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう。リフレッシュしてくるわね</t>
+          <t xml:space="preserve">メディア出演…？ 楽しみだわ</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.seductive.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6101,7 +6057,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.seductive.normal[1]</t>
+          <t xml:space="preserve">party.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6111,14 +6067,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう。早く戻れるように頑張るわ</t>
+          <t xml:space="preserve">楽しかったわ。こういう時間もいいわね</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.seductive.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6133,7 +6089,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.seductive.normal[1]</t>
+          <t xml:space="preserve">refresh_leave.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6143,14 +6099,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">しっかり吸収させてもらうわね</t>
+          <t xml:space="preserve">ありがとう。リフレッシュしてくるわね</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.seductive.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6160,12 +6116,12 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.seductive.normal[1]</t>
+          <t xml:space="preserve">special_treatment.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6175,14 +6131,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">メディア出演のお話？ 楽しみだわ</t>
+          <t xml:space="preserve">ありがとう。早く戻れるように頑張るわ</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.seductive.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6192,12 +6148,12 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E4.seductive.normal[1]</t>
+          <t xml:space="preserve">trainer.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6207,14 +6163,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新しいスカウトのお話が来てるみたいよ</t>
+          <t xml:space="preserve">しっかり吸収させてもらうわね</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.seductive.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6229,7 +6185,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.seductive.normal[1]</t>
+          <t xml:space="preserve">E1.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6239,14 +6195,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">他の団体からお誘いが来てるの</t>
+          <t xml:space="preserve">メディア出演のお話？ 楽しみだわ</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6261,7 +6217,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.seductive.normal[1]</t>
+          <t xml:space="preserve">E4.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6271,14 +6227,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさいね…今日はちょっと、気持ちが入らなくて</t>
+          <t xml:space="preserve">新しいスカウトのお話が来てるみたいよ</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.seductive.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6293,7 +6249,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.seductive.normal[1]</t>
+          <t xml:space="preserve">E6.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6303,14 +6259,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（「最近、ここにいる意味あるのかしら」と同僚に漏らしている）</t>
+          <t xml:space="preserve">他の団体からお誘いが来てるの</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.seductive.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6325,7 +6281,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.seductive.normal[1]</t>
+          <t xml:space="preserve">S_boycott.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6335,14 +6291,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「次のステージが待っているかも」と匂わせ投稿）</t>
+          <t xml:space="preserve">ごめんなさいね…今日はちょっと、気持ちが入らなくて</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.seductive.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6357,7 +6313,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.seductive.normal[1]</t>
+          <t xml:space="preserve">S_grumble.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6367,14 +6323,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">タイトルマッチの機会、いただけないかしら</t>
+          <t xml:space="preserve">（「最近、ここにいる意味あるのかしら」と同僚に漏らしている）</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.seductive.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6389,7 +6345,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.seductive.normal[1]</t>
+          <t xml:space="preserve">S_sns.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6399,14 +6355,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人との試合、組んでもらえないかしら</t>
+          <t xml:space="preserve">（SNSに「次のステージが待っているかも」と匂わせ投稿）</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.seductive.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6421,7 +6377,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.seductive.normal[1]</t>
+          <t xml:space="preserve">S1.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6431,14 +6387,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少し休ませてもらえないかしら…</t>
+          <t xml:space="preserve">タイトルマッチの機会、いただけないかしら</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.seductive.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6453,7 +6409,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.seductive.normal[1]</t>
+          <t xml:space="preserve">S2.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6463,14 +6419,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このままじゃ困るわ。ちゃんと考えてもらえないかしら</t>
+          <t xml:space="preserve">あの人との試合、組んでもらえないかしら</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.seductive.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6485,7 +6441,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.seductive.normal[1]</t>
+          <t xml:space="preserve">S3.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6495,14 +6451,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…（沈黙）…ううん、なんでもないの</t>
+          <t xml:space="preserve">少し休ませてもらえないかしら…</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.seductive.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6517,7 +6473,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.seductive.normal[1]</t>
+          <t xml:space="preserve">S4_direct.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6527,14 +6483,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">特訓させてもらえないかしら？</t>
+          <t xml:space="preserve">このままじゃ困るわ。ちゃんと考えてもらえないかしら</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.seductive.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6549,7 +6505,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.seductive.normal[1]</t>
+          <t xml:space="preserve">S4_silent.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6559,14 +6515,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の指導、私にやらせてもらえないかしら</t>
+          <t xml:space="preserve">…（沈黙）…ううん、なんでもないの</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.seductive.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6576,12 +6532,12 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.seductive.normal[1]</t>
+          <t xml:space="preserve">S5.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6591,14 +6547,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し時間がかかりそう。ごめんなさいね</t>
+          <t xml:space="preserve">特訓させてもらえないかしら？</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.seductive.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6608,12 +6564,12 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.seductive.normal[1]</t>
+          <t xml:space="preserve">S6.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6623,14 +6579,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人とはもう無理よ。何とかしてもらえないかしら</t>
+          <t xml:space="preserve">後輩の指導、私にやらせてもらえないかしら</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.seductive.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6645,7 +6601,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.seductive.normal[1]</t>
+          <t xml:space="preserve">B1.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6655,14 +6611,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">向こうにも非があるのに…私だけが悪いの？</t>
+          <t xml:space="preserve">…少し時間がかかりそう。ごめんなさいね</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.seductive.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6677,7 +6633,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.seductive.normal[1]</t>
+          <t xml:space="preserve">B2_fighter1.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6687,14 +6643,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私のイメージに合うブランドね。いい選択だわ♡</t>
+          <t xml:space="preserve">あの人とはもう無理よ。何とかしてもらえないかしら</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.seductive.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6709,7 +6665,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.seductive.normal[1]</t>
+          <t xml:space="preserve">B2_fighter2.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6719,14 +6675,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">カメラの前ね…いい絵、撮らせてあげる♡</t>
+          <t xml:space="preserve">向こうにも非があるのに…私だけが悪いの？</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.seductive.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6741,7 +6697,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.seductive.normal[1]</t>
+          <t xml:space="preserve">B4_brand.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6751,14 +6707,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンと直接会える機会ね…喜ばせてあげるわ♡</t>
+          <t xml:space="preserve">私のイメージに合うブランドね。いい選択だわ♡</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.seductive.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6773,7 +6729,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.seductive.normal[1]</t>
+          <t xml:space="preserve">B4_cm.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6783,14 +6739,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ランウェイか…私の本領発揮ね♡</t>
+          <t xml:space="preserve">カメラの前ね…いい絵、撮らせてあげる♡</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.seductive.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6805,7 +6761,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.seductive.normal[1]</t>
+          <t xml:space="preserve">B4_fan.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6815,14 +6771,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">グラビアね…全部見せてあげるわ♡</t>
+          <t xml:space="preserve">ファンと直接会える機会ね…喜ばせてあげるわ♡</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.seductive.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6837,7 +6793,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.seductive.normal[1]</t>
+          <t xml:space="preserve">B4_fashion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6847,14 +6803,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バラエティか。じゃあ、素の私を少し見せてあげようかな</t>
+          <t xml:space="preserve">ランウェイか…私の本領発揮ね♡</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.seductive.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6869,7 +6825,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.seductive.normal[1]</t>
+          <t xml:space="preserve">B4_gravure.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6879,14 +6835,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">取材ね…いい姿を見せてあげるわ</t>
+          <t xml:space="preserve">グラビアね…全部見せてあげるわ♡</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6896,29 +6852,29 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">B4_variety.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでくれるなら…期待に応えるわよ</t>
+          <t xml:space="preserve">バラエティねぇ。じゃあ、素の私を少し見せてあげようかしら</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6928,29 +6884,29 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">B4.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくね。期待に応えてあげる</t>
+          <t xml:space="preserve">取材ね…いい姿を見せてあげるわ</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.normal[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6960,12 +6916,12 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[2]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6975,14 +6931,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、選んでくれてありがとう</t>
+          <t xml:space="preserve">選んでくれるなら…期待に応えるわよ</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6992,7 +6948,7 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
@@ -7007,14 +6963,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくね。力になるわ</t>
+          <t xml:space="preserve">よろしくね。期待に応えてあげる</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7024,12 +6980,12 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7039,14 +6995,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくね。精一杯やるわ</t>
+          <t xml:space="preserve">ふふ、選んでくれてありがとう</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7056,7 +7012,7 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
@@ -7071,14 +7027,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ちょっとだけ、休ませてね</t>
+          <t xml:space="preserve">よろしくね。力になるわ</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.normal[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7088,12 +7044,12 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[2]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7103,14 +7059,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すぐに戻るわ。待っててくれる？</t>
+          <t xml:space="preserve">よろしくね。精一杯やるわ</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7120,12 +7076,12 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7135,14 +7091,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでくれるなら…期待に応えるわよ</t>
+          <t xml:space="preserve">…ちょっとだけ、休ませてね</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7152,12 +7108,12 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7167,14 +7123,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくね。期待に応えてあげる</t>
+          <t xml:space="preserve">すぐに戻るわ。待っててくれる？</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7189,7 +7145,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.seductive.normal[2]</t>
+          <t xml:space="preserve">draftInterest.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7199,14 +7155,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、選んでくれてありがとう</t>
+          <t xml:space="preserve">選んでくれるなら…期待に応えるわよ</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7221,7 +7177,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.seductive.normal[1]</t>
+          <t xml:space="preserve">draftJoin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7231,14 +7187,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">落ちこぼれを拾うなんて。…物好きね。</t>
+          <t xml:space="preserve">よろしくね。期待に応えてあげる</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7253,7 +7209,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.seductive.normal[1]</t>
+          <t xml:space="preserve">draftJoin.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7263,14 +7219,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくね。力になるわ</t>
+          <t xml:space="preserve">ふふ、選んでくれてありがとう</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7285,7 +7241,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.seductive.normal[1]</t>
+          <t xml:space="preserve">faGreeting.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7295,14 +7251,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくね。精一杯やるわ</t>
+          <t xml:space="preserve">わざわざ口説きに来るなんて。…物好きね、あなた。</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7317,7 +7273,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.seductive.normal[1]</t>
+          <t xml:space="preserve">faSigning.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7327,14 +7283,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ちょっとだけ、休ませてね</t>
+          <t xml:space="preserve">よろしくね。力になるわ</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7349,7 +7305,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.seductive.normal[2]</t>
+          <t xml:space="preserve">faWelcome.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7359,14 +7315,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すぐに戻るわ。待っててくれる？</t>
+          <t xml:space="preserve">よろしくね。精一杯やるわ</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7381,7 +7337,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.seductive.normal[1]</t>
+          <t xml:space="preserve">injury.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7391,14 +7347,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここでの思い出、大切にするわ</t>
+          <t xml:space="preserve">…ちょっとだけ、休ませてね</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7413,7 +7369,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.seductive.normal[2]</t>
+          <t xml:space="preserve">injury.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7423,14 +7379,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お世話になりました。また、どこかで</t>
+          <t xml:space="preserve">すぐに戻るわ。待っててくれる？</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7445,7 +7401,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.seductive.normal[1]</t>
+          <t xml:space="preserve">release.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7455,14 +7411,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間だけど、よろしくね</t>
+          <t xml:space="preserve">ここでの思い出、大切にするわ</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7477,7 +7433,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.seductive.normal[1]</t>
+          <t xml:space="preserve">release.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7487,14 +7443,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">目をつけたのはそっち。…責任、取ってね</t>
+          <t xml:space="preserve">お世話になりました。また、どこかで</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7509,7 +7465,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.seductive.normal[1]</t>
+          <t xml:space="preserve">rentalGreeting.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7519,14 +7475,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいわ…でも、次こそはね</t>
+          <t xml:space="preserve">短い間だけど、よろしくね</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7541,7 +7497,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.seductive.normal[1]</t>
+          <t xml:space="preserve">scoutGreeting.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7551,14 +7507,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛成功…。このベルト、まだ返す気はないわ</t>
+          <t xml:space="preserve">目をつけたのはそっち。…責任、取ってね</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7573,7 +7529,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.seductive.normal[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7583,14 +7539,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトがない景色なんて…でも、ここで終わらないわ</t>
+          <t xml:space="preserve">悔しいわ…でも、次こそはね</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7605,7 +7561,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.seductive.normal[1]</t>
+          <t xml:space="preserve">titleDefense.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7615,14 +7571,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオン…最高の気分ね</t>
+          <t xml:space="preserve">防衛成功…。このベルト、まだ返す気はないわ</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7632,12 +7588,12 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">titleLoss.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7647,14 +7603,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここでの思い出、大切にするわ</t>
+          <t xml:space="preserve">ベルトがない景色なんて…でも、ここで終わらないわ</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7664,12 +7620,12 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[2]</t>
+          <t xml:space="preserve">titleWin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7679,14 +7635,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お世話になりました。また、どこかで</t>
+          <t xml:space="preserve">チャンピオン…最高の気分ね</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7696,7 +7652,7 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
@@ -7711,14 +7667,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間だけど、よろしくね</t>
+          <t xml:space="preserve">ここでの思い出、大切にするわ</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7728,12 +7684,12 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7743,14 +7699,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいわ…でも、次こそはね</t>
+          <t xml:space="preserve">お世話になりました。また、どこかで</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7760,7 +7716,7 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
@@ -7775,14 +7731,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛成功…。このベルト、まだ返す気はないわ</t>
+          <t xml:space="preserve">短い間だけど、よろしくね</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7792,7 +7748,7 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
@@ -7807,14 +7763,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトがない景色なんて…でも、ここで終わらないわ</t>
+          <t xml:space="preserve">悔しいわ…でも、次こそはね</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7824,7 +7780,7 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
@@ -7839,14 +7795,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオン…最高の気分ね</t>
+          <t xml:space="preserve">防衛成功…。このベルト、まだ返す気はないわ</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7856,29 +7812,29 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう…合わないみたいね</t>
+          <t xml:space="preserve">ベルトがない景色なんて…でも、ここで終わらないわ</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7888,29 +7844,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近どこか冷たいわ…気のせいかしら</t>
+          <t xml:space="preserve">チャンピオン…最高の気分ね</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7925,7 +7881,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.normal.seductive[1]</t>
+          <t xml:space="preserve">bond_39_down.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7935,14 +7891,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なかなか面白い人ね。もっと近くで見ていたい</t>
+          <t xml:space="preserve">もう…合わないみたいね</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7957,7 +7913,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.normal.seductive[1]</t>
+          <t xml:space="preserve">bond_59_down.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7967,14 +7923,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">特別な存在。他の誰とも違うの</t>
+          <t xml:space="preserve">最近どこか冷たいわ…気のせいかしら</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7989,7 +7945,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.normal.seductive[1]</t>
+          <t xml:space="preserve">bond_60_up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7999,14 +7955,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もういいかしら。次を探さなきゃ</t>
+          <t xml:space="preserve">なかなか面白い人ね。もっと近くで見ていたい</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -8021,7 +7977,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.normal.seductive[1]</t>
+          <t xml:space="preserve">bond_80_up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8031,14 +7987,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気になるわ…潰しがいがありそうね</t>
+          <t xml:space="preserve">特別な存在。他の誰とも違うの</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8053,7 +8009,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.normal.seductive[1]</t>
+          <t xml:space="preserve">rivalry_29_down.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8063,14 +8019,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうしても許せない。必ず私が勝つわ</t>
+          <t xml:space="preserve">もういいかしら。次を探さなきゃ</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8085,7 +8041,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.normal.seductive[1]</t>
+          <t xml:space="preserve">rivalry_30_up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8095,14 +8051,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私の全て…最高の獲物よ</t>
+          <t xml:space="preserve">気になるわ…潰しがいがありそうね</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8117,7 +8073,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.normal.seductive[1]</t>
+          <t xml:space="preserve">rivalry_50_up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8127,14 +8083,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここでなら…私らしくいられるわ</t>
+          <t xml:space="preserve">どうしても許せない。必ず私が勝つわ</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8149,7 +8105,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.normal.seductive[1]</t>
+          <t xml:space="preserve">rivalry_70_up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8159,14 +8115,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここにはもう何も残ってないわ</t>
+          <t xml:space="preserve">私の全て…最高の獲物よ</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8181,7 +8137,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.normal.seductive[1]</t>
+          <t xml:space="preserve">trust_above_75.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8191,14 +8147,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここにいる意味…本当にあるのかしら</t>
+          <t xml:space="preserve">ここでなら…私らしくいられるわ</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8208,12 +8164,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.seductive.normal[1]</t>
+          <t xml:space="preserve">trust_below_20.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8223,14 +8179,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けは負け。でも…悪くない戦いだったわ</t>
+          <t xml:space="preserve">ここにはもう何も残ってないわ</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8240,12 +8196,12 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.seductive.normal[1]</t>
+          <t xml:space="preserve">trust_below_35.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8255,14 +8211,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">完璧な夜ね…最高の気分だわ</t>
+          <t xml:space="preserve">ここにいる意味…本当にあるのかしら</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8277,7 +8233,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8287,14 +8243,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたのね…屈辱だわ</t>
+          <t xml:space="preserve">負けは負け。でも…悪くない戦いだったわ</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8309,7 +8265,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8319,14 +8275,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、今日も勝ち。気分がいいわ</t>
+          <t xml:space="preserve">完璧な夜ね…最高の気分だわ</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8341,7 +8297,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-01.loss.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8351,14 +8307,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">汗を流すのも悪くないわね</t>
+          <t xml:space="preserve">負けたのね…屈辱だわ</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8373,7 +8329,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-01.win.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8383,14 +8339,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ねぇ…最近私のこと放置してない？</t>
+          <t xml:space="preserve">ふふ、今日も勝ち。気分がいいわ</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8405,7 +8361,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-02.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8415,14 +8371,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近いい扱い受けてる気がするわ。嬉しいわね</t>
+          <t xml:space="preserve">汗を流すのも悪くないわね</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8437,7 +8393,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-03.down.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8447,14 +8403,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと気になってるの。いい距離感よね</t>
+          <t xml:space="preserve">ねぇ…最近私のこと放置してない？</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8469,7 +8425,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-03.up.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8479,14 +8435,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…考えちゃうのよね</t>
+          <t xml:space="preserve">最近いい扱い受けてる気がするわ。嬉しいわね</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8501,7 +8457,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-04.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8511,14 +8467,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を干すつもり？ もったいないと思うけど</t>
+          <t xml:space="preserve">ちょっと気になってるの。いい距離感よね</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8533,7 +8489,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-05.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8543,14 +8499,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体が言うこと聞かないわ…もどかしい</t>
+          <t xml:space="preserve">…考えちゃうのよね</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8565,7 +8521,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-06.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8575,14 +8531,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負け続き…こんなの私じゃないわ</t>
+          <t xml:space="preserve">私を干すつもり？ もったいないと思うけど</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8597,7 +8553,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-07.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8607,14 +8563,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近負けなしよ。ふふ、誰が相手でも返り討ちだわ</t>
+          <t xml:space="preserve">体が言うこと聞かないわ…もどかしい</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8629,7 +8585,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-08.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8639,14 +8595,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">退屈…早くリングに立ちたいわ</t>
+          <t xml:space="preserve">負け続き…こんなの私じゃないわ</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8661,7 +8617,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-09.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8671,14 +8627,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いたわね、そういえば。……それだけよ</t>
+          <t xml:space="preserve">最近負けなしよ。ふふ、誰が相手でも返り討ちだわ</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8688,12 +8644,12 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">GL-10.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8703,14 +8659,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、いつもの私に戻ったみたい。でも悪くない気分よ</t>
+          <t xml:space="preserve">退屈…早くリングに立ちたいわ</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8720,29 +8676,29 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-11.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体、まだ震えてるの。でも…この傷ごと、最後の舞台に上がるわ</t>
+          <t xml:space="preserve">いたわね、そういえば。……それだけよ</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8752,29 +8708,29 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.normal[2]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぼろぼろでしょ、私。でもね…一番きれいに終わらせるのは、こういう時よ</t>
+          <t xml:space="preserve">あら、いつもの私に戻ったみたい。でも悪くない気分よ</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8789,7 +8745,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.normal[1]</t>
+          <t xml:space="preserve">preFinal.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8799,14 +8755,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">来るなら誰でもいいわ。全部、受け止めてあげる</t>
+          <t xml:space="preserve">身体、まだ震えてるの。でも…この傷ごと、最後の舞台に上がるわ</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8821,7 +8777,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.normal[2]</t>
+          <t xml:space="preserve">preFinal.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8831,14 +8787,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この一戦、たっぷり付き合ってもらうわよ。逃がさないから</t>
+          <t xml:space="preserve">ぼろぼろでしょ、私。でもね…一番きれいに終わらせるのは、こういう時よ</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8853,7 +8809,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.normal[1]</t>
+          <t xml:space="preserve">preMatch.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8863,14 +8819,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、落としたわ。…息、荒いでしょ? でも、まだ物足りないの。次、出してよ</t>
+          <t xml:space="preserve">来るなら誰でもいいわ。全部、受け止めてあげる</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8885,7 +8841,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.normal[2]</t>
+          <t xml:space="preserve">preMatch.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8895,14 +8851,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってるの。次の子、早くいらっしゃい。ここは、渡さないから</t>
+          <t xml:space="preserve">この一戦、たっぷり付き合ってもらうわよ。逃がさないから</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8912,12 +8868,12 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.normal[1]</t>
+          <t xml:space="preserve">survivor.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8927,14 +8883,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で勝ったのよ。この勝利は、一人じゃ味わえない特別なもの</t>
+          <t xml:space="preserve">一人、落としたわ。…息、荒いでしょ？ でも、まだ物足りないの。次、出してよ</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8944,12 +8900,12 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.normal[2]</t>
+          <t xml:space="preserve">survivor.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8959,14 +8915,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が繋いでくれた……その信頼に応えられたなら、嬉しいわ</t>
+          <t xml:space="preserve">まだ立ってるの。次の子、早くいらっしゃい。ここは、渡さないから</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8981,7 +8937,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.normal[1]</t>
+          <t xml:space="preserve">champion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8991,14 +8947,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">個人賞……嬉しくないとは言わない。でも、欲しかったのはこれじゃないの</t>
+          <t xml:space="preserve">三人で勝ったのよ。この勝利は、一人じゃ味わえない特別なもの</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -9013,7 +8969,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.normal[2]</t>
+          <t xml:space="preserve">champion.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9023,14 +8979,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次は団体ごと勝つわ。そうでなきゃ……意味がないもの</t>
+          <t xml:space="preserve">仲間が繋いでくれた……その信頼に応えられたなら、嬉しいわ</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9045,7 +9001,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.normal[1]</t>
+          <t xml:space="preserve">defiant.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9055,14 +9011,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ震えてるの、身体。でもね、この汗と痛みが……今日の私を証明してくれてる</t>
+          <t xml:space="preserve">個人賞……嬉しくないとは言わない。でも、欲しかったのはこれじゃないの</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9077,7 +9033,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.normal[2]</t>
+          <t xml:space="preserve">defiant.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9087,14 +9043,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">倒しても倒しても来るの。でも、最後に立ってたのはこっち。悪くないでしょ？</t>
+          <t xml:space="preserve">次は団体ごと勝つわ。そうでなきゃ……意味がないもの</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9104,12 +9060,12 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.normal[1]</t>
+          <t xml:space="preserve">gauntlet.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9119,14 +9075,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝。…最高の気分ね</t>
+          <t xml:space="preserve">まだ震えてるの、身体。でもね、この汗と痛みが……今日の私を証明してくれてる</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9136,12 +9092,12 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.normal[2]</t>
+          <t xml:space="preserve">gauntlet.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9151,14 +9107,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、これで終わりじゃないわよ</t>
+          <t xml:space="preserve">倒しても倒しても来るの。でも、最後に立ってたのはこっち。悪くないでしょ？</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9173,7 +9129,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.seductive.normal[1]</t>
+          <t xml:space="preserve">champion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9183,14 +9139,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、残念ね。でも次があるわ</t>
+          <t xml:space="preserve">優勝。…最高の気分ね</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9205,7 +9161,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.seductive.normal[2]</t>
+          <t xml:space="preserve">champion.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9215,14 +9171,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいけど…いい経験だったわ</t>
+          <t xml:space="preserve">ふふ、これで終わりじゃないわよ</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9237,7 +9193,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.seductive.normal[1]</t>
+          <t xml:space="preserve">postLose.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9247,14 +9203,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、まずは一勝ね。次も魅せてあげるわ</t>
+          <t xml:space="preserve">あら、残念ね。でも次があるわ</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9269,7 +9225,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.seductive.normal[2]</t>
+          <t xml:space="preserve">postLose.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9279,14 +9235,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てたわ。……でもまだ先がある</t>
+          <t xml:space="preserve">悔しいけど…いい経験だったわ</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9301,7 +9257,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.seductive.normal[1]</t>
+          <t xml:space="preserve">postMatchWin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9311,14 +9267,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい経験だったわ。もっと魅せられるようになりたいわね</t>
+          <t xml:space="preserve">ふふ、まずは一勝ね。次も魅せてあげるわ</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9333,7 +9289,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.seductive.normal[2]</t>
+          <t xml:space="preserve">postMatchWin.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9343,14 +9299,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだこんなものじゃないわよ</t>
+          <t xml:space="preserve">勝てたわ。……でもまだ先がある</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9365,7 +9321,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.normal[1]</t>
+          <t xml:space="preserve">postWin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9375,14 +9331,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝…。最後の舞台、最高に魅せてあげるわ</t>
+          <t xml:space="preserve">いい経験だったわ。もっと魅せられるようになりたいわね</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9397,7 +9353,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.normal[2]</t>
+          <t xml:space="preserve">postWin.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9407,14 +9363,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あと一つ。全てを懸けるわ</t>
+          <t xml:space="preserve">まだまだこんなものじゃないわよ</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9429,7 +9385,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.normal[1]</t>
+          <t xml:space="preserve">preFinal.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9439,14 +9395,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次の相手…楽しみね</t>
+          <t xml:space="preserve">決勝…。最後の舞台、最高に魅せてあげるわ</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9461,7 +9417,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.normal[2]</t>
+          <t xml:space="preserve">preFinal.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9471,14 +9427,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしの魅力、見せつけてあげる</t>
+          <t xml:space="preserve">あと一つ。全てを懸けるわ</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9493,7 +9449,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.seductive.normal[1]</t>
+          <t xml:space="preserve">preMatch.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9503,14 +9459,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">出場が決まったわ。見ていてね</t>
+          <t xml:space="preserve">次の相手…楽しみね</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9525,7 +9481,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.seductive.normal[2]</t>
+          <t xml:space="preserve">preMatch.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9535,14 +9491,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">素敵な舞台ね。魅せてあげるわ</t>
+          <t xml:space="preserve">私の魅力、見せつけてあげる</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9552,12 +9508,12 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">summon.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9567,14 +9523,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は負けるわけにはいかないの。覚悟してね</t>
+          <t xml:space="preserve">出場が決まったわ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9584,12 +9540,12 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">summon.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9599,14 +9555,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ……最高の舞台で、最高の結末。悪くないわね</t>
+          <t xml:space="preserve">素敵な舞台ね。魅せてあげるわ</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.normal[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9616,12 +9572,12 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[2]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9631,14 +9587,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見ててくれた？ これが私のすべてよ</t>
+          <t xml:space="preserve">今日は負けるわけにはいかないの。覚悟してね</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.normal[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9648,7 +9604,7 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
@@ -9663,14 +9619,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ、おたくの団体さん…少し気になってたの</t>
+          <t xml:space="preserve">ふふ……最高の舞台で、最高の結末。悪くないわね</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.normal[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9680,7 +9636,7 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
@@ -9695,14 +9651,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">遊んであげるわ。……本気でね</t>
+          <t xml:space="preserve">見ててくれた？ これが私のすべてよ</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.normal[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9712,7 +9668,7 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
@@ -9727,14 +9683,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら…怖いのかしら。可哀想</t>
+          <t xml:space="preserve">うふふ、おたくの団体さん…少し気になってたの</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.normal[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9744,7 +9700,7 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
@@ -9759,14 +9715,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃げるのね…。つまらないわ</t>
+          <t xml:space="preserve">遊んであげるわ。……本気でね</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.normal[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9776,12 +9732,12 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9791,14 +9747,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃったわね…悔しい</t>
+          <t xml:space="preserve">あら…怖いのかしら。可哀想</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.normal[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9808,12 +9764,12 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.seductive.normal[2]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9823,14 +9779,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次はもっと綺麗に勝ってみせるわ</t>
+          <t xml:space="preserve">逃げるのね…。つまらないわ</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.normal[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9845,7 +9801,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.seductive.normal[1]</t>
+          <t xml:space="preserve">result_lose.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9855,14 +9811,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、勝てたわね。素敵な対抗戦だったわ</t>
+          <t xml:space="preserve">負けちゃったわね…悔しい</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.normal[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9877,7 +9833,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.seductive.normal[2]</t>
+          <t xml:space="preserve">result_lose.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9887,14 +9843,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝利の味は…格別ね</t>
+          <t xml:space="preserve">次はもっと綺麗に勝ってみせるわ</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9904,12 +9860,12 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">result_win.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9919,14 +9875,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、もう終わり？ 物足りなかったわ</t>
+          <t xml:space="preserve">ふふ、勝てたわね。素敵な対抗戦だったわ</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.normal[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9936,12 +9892,12 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[2]</t>
+          <t xml:space="preserve">result_win.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9951,14 +9907,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うちの団体の底力、見せてあげたわよ</t>
+          <t xml:space="preserve">勝利の味は…格別ね</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.normal[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9973,7 +9929,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[3]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9983,14 +9939,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、うちの団体の魅力、わかっていただけたかしら</t>
+          <t xml:space="preserve">あら、もう終わり？ 物足りなかったわ</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.seductive.normal[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -10000,29 +9956,29 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来れたのね…最高の気分だわ</t>
+          <t xml:space="preserve">うちの団体の底力、見せてあげたわよ</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.normal[3]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10032,59 +9988,123 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[3]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">落ちこぼれを拾うなんて。…物好きね。</t>
+          <t xml:space="preserve">ふふ、うちの団体の魅力、わかっていただけたかしら</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.seductive.normal[1]</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.seductive.normal[1]</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここまで来れたのね…最高の気分だわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="40" customHeight="1">
+      <c r="A305" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.seductive.normal[1]</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.normal[1]</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わざわざ口説きに来るなんて。…物好きね、あなた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="40" customHeight="1">
+      <c r="A306" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.seductive.normal[1]</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr" s="2">
+      <c r="B306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr" s="12">
+      <c r="D306" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
-      <c r="E304" t="inlineStr" s="2">
+      <c r="E306" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F304" t="inlineStr" s="3">
+      <c r="F306" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">目をつけたのはそっち。…責任、取ってね</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H304"/>
+  <autoFilter ref="A1:H306"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/蠱惑×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×ノーマル.xlsx
@@ -284,7 +284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H306"/>
+  <dimension ref="A1:H313"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -4182,7 +4182,7 @@
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.seductive.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_accept.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.seductive.normal[1]</t>
+          <t xml:space="preserve">decline_accept.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4207,14 +4207,14 @@
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがと、社長♡ もっと魅せてあげるわね。</t>
+          <t xml:space="preserve">ええ、それでいいの。……安く抱えられるうちに、せいぜい使ってちょうだい。</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.seductive.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_hold.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.seductive.normal[1]</t>
+          <t xml:space="preserve">decline_hold.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4239,14 +4239,14 @@
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少しでも考えてくれたのね。…ありがと♡</t>
+          <t xml:space="preserve">あら……身銭を切ったのね。……ふふ、その甘さ、高くつくわよ？　ちゃんと返すもの。</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.seductive.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_open.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.seductive.normal[1]</t>
+          <t xml:space="preserve">decline_open.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4271,14 +4271,14 @@
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう。残念ね。</t>
+          <t xml:space="preserve">あら、そんな顔をしないで。{tenure}数字が正直なだけでしょう？　……嫌いじゃないわ、その正直さ。</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.seductive.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_strict.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.seductive.normal[1]</t>
+          <t xml:space="preserve">decline_strict.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4303,14 +4303,14 @@
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、ちょっといい？ {tenure}{record}…もう少しだけ、考えてくれない？</t>
+          <t xml:space="preserve">……あら。そこまで削るのね。……ええ、覚えておくわ。数字は、忘れてくれないもの。</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.seductive.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_accept.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.seductive.normal[1]</t>
+          <t xml:space="preserve">decline_voluntary_accept.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4335,14 +4335,14 @@
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう。残念だけど…仕方ないわね。</t>
+          <t xml:space="preserve">それで手を打ちましょう。……値札が軽くなったぶん、身のこなしも軽くなりそうだわ。</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_hold.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.seductive.normal[1]</t>
+          <t xml:space="preserve">decline_voluntary_hold.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4367,14 +4367,14 @@
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、手短に言うわ。辞めます。もう決めたの。</t>
+          <t xml:space="preserve">……下げないの？　……ずるいことをするのね。……これじゃ、辞めるに辞められないじゃない。</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.normal[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_open.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.seductive.normal[2]</t>
+          <t xml:space="preserve">decline_voluntary_open.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4399,14 +4399,14 @@
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お世話になったわ。でも、もうここでは続けられないの。</t>
+          <t xml:space="preserve">社長、先に言わせて。{tenure}……全盛期は過ぎたわ。下げていいの。まだ、ここにいたいから。</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.seductive.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.seductive.normal[1]</t>
+          <t xml:space="preserve">raise_accept.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4431,14 +4431,14 @@
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">聞いてくれるの？ {record}…新しい場所で、自分を試してみたいの。</t>
+          <t xml:space="preserve">ありがと、社長♡ もっと魅せてあげるわね。</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.seductive.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.seductive.normal[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4463,14 +4463,14 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長…ごめんなさい。{tenure}ここを離れたいの。</t>
+          <t xml:space="preserve">少しでも考えてくれたのね。…ありがと♡</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.seductive.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.seductive.normal[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4495,14 +4495,14 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう。{tenure_farewell}{rivalry}元気でね。</t>
+          <t xml:space="preserve">……そう。残念ね。</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.seductive.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.seductive.normal[1]</t>
+          <t xml:space="preserve">raise_open.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4527,14 +4527,14 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう。でも…もう決めたの。ごめんね。</t>
+          <t xml:space="preserve">社長、ちょっといい？ {tenure}{record}…もう少しだけ、考えてくれない？</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.seductive.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.seductive.normal[1]</t>
+          <t xml:space="preserve">raise_refuse.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4559,370 +4559,370 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そこまでしてくれるの？ …もう少しだけ、いてあげる♡</t>
+          <t xml:space="preserve">……そう。残念だけど…仕方ないわね。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.normal[1]</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.seductive.normal[1]</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長、手短に言うわ。辞めます。もう決めたの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="40" customHeight="1">
+      <c r="A135" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.normal[2]</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.seductive.normal[2]</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お世話になったわ。でも、もうここでは続けられないの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="40" customHeight="1">
+      <c r="A136" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.seductive.normal[1]</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_listen.seductive.normal[1]</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">聞いてくれるの？ {record}…新しい場所で、自分を試してみたいの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="40" customHeight="1">
+      <c r="A137" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.seductive.normal[1]</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.seductive.normal[1]</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長…ごめんなさい。{tenure}ここを離れたいの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="40" customHeight="1">
+      <c r="A138" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.seductive.normal[1]</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.seductive.normal[1]</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……そう。{tenure_farewell}{rivalry}元気でね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="40" customHeight="1">
+      <c r="A139" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.seductive.normal[1]</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.seductive.normal[1]</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ありがとう。でも…もう決めたの。ごめんね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="40" customHeight="1">
+      <c r="A140" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.seductive.normal[1]</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.seductive.normal[1]</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……そこまでしてくれるの？ …もう少しだけ、いてあげる♡</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="40" customHeight="1">
+      <c r="A141" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.seductive.normal[1]</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr" s="2">
+      <c r="B141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr" s="12">
+      <c r="D141" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.seductive.normal[1]</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr" s="2">
+      <c r="E141" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr" s="3">
+      <c r="F141" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">うれしいお誘いだけど…今の仲間を置いていく気にはなれないわ。
 ごめんなさい</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="40" customHeight="1">
-      <c r="A135" t="inlineStr" s="15">
+    <row r="142" ht="40" customHeight="1">
+      <c r="A142" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.fail.seductive.normal[1]</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr" s="2">
+      <c r="B142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr" s="12">
+      <c r="D142" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fail.seductive.normal[1]</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr" s="2">
+      <c r="E142" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr" s="3">
+      <c r="F142" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ごめんなさい、今回はパス。
 縁があればまたね</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="40" customHeight="1">
-      <c r="A136" t="inlineStr" s="15">
+    <row r="143" ht="40" customHeight="1">
+      <c r="A143" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.start.seductive.normal[1]</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr" s="2">
+      <c r="B143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr" s="12">
+      <c r="D143" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">start.seductive.normal[1]</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr" s="2">
+      <c r="E143" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr" s="3">
+      <c r="F143" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">私を誘うの？
 ふふ…条件次第ね</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="40" customHeight="1">
-      <c r="A137" t="inlineStr" s="15">
+    <row r="144" ht="40" customHeight="1">
+      <c r="A144" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.success.seductive.normal[1]</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr" s="2">
+      <c r="B144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr" s="12">
+      <c r="D144" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">success.seductive.normal[1]</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr" s="2">
+      <c r="E144" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr" s="3">
+      <c r="F144" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…わかったわ、行く。
 実力で居場所を作ってみせるわ</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="40" customHeight="1">
-      <c r="A138" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.seductive.normal[1]</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">あら…何かが変わった気がするわ</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="40" customHeight="1">
-      <c r="A139" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">BT_HINT_LINES.seductive.normal[1]</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">何かが変わり始めてる…自分でもわかるわ</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="40" customHeight="1">
-      <c r="A140" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.seductive.normal[1]</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">cap_reached.seductive.normal[1]</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">これ以上は…ね。でも、十分よ</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="40" customHeight="1">
-      <c r="A141" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.seductive.normal[1]</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ovr_elite.seductive.normal[1]</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ここまで来ちゃったのね…ふふ</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="40" customHeight="1">
-      <c r="A142" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.seductive.normal[1]</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ovr_growth.seductive.normal[1]</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ふふ、ちょっとは良くなったかしら</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="40" customHeight="1">
-      <c r="A143" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.seductive.normal[1]</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ovr_legend.seductive.normal[1]</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ここまで来たら…もう怖いものなんてないわ</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="40" customHeight="1">
-      <c r="A144" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.seductive.normal[1]</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">pop_growth.seductive.normal[1]</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ふふ、注目されるのは悪くないわね</t>
-        </is>
-      </c>
-    </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.seductive.normal[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4932,12 +4932,12 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4947,14 +4947,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなにたくさん…みんなの視線が気持ちいいわ</t>
+          <t xml:space="preserve">あら…何かが変わった気がするわ</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
@@ -4979,14 +4979,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何のために闘ってるのかしら…わからなくなったわ</t>
+          <t xml:space="preserve">何かが変わり始めてる…自分でもわかるわ</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4996,12 +4996,12 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">cap_reached.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5011,14 +5011,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだやれるわ…やってみせる</t>
+          <t xml:space="preserve">これ以上は…ね。でも、十分よ</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5028,12 +5028,12 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">ovr_elite.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5043,14 +5043,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっと…戻ってこれたわ</t>
+          <t xml:space="preserve">ここまで来ちゃったのね…ふふ</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.seductive.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5060,12 +5060,12 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.seductive.normal[1]</t>
+          <t xml:space="preserve">ovr_growth.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5075,14 +5075,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの負けから…何かがおかしいの</t>
+          <t xml:space="preserve">ふふ、ちょっとは良くなったかしら</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.seductive.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.seductive.normal[1]</t>
+          <t xml:space="preserve">ovr_legend.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5107,14 +5107,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体は治ったはずなのに…ね、動けないの</t>
+          <t xml:space="preserve">ここまで来たら…もう怖いものなんてないわ</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.seductive.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.seductive.normal[1]</t>
+          <t xml:space="preserve">pop_growth.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5139,14 +5139,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">戻ってこれたのに…怖いの</t>
+          <t xml:space="preserve">ふふ、注目されるのは悪くないわね</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.seductive.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.seductive.normal[1]</t>
+          <t xml:space="preserve">pop_star.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5171,14 +5171,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我は治ったのに…気力が戻らないの</t>
+          <t xml:space="preserve">こんなにたくさん…みんなの視線が気持ちいいわ</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.seductive.normal[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5188,29 +5188,29 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">autumnWarChampion.seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の名を背負うなら、このくらい華やかに勝たなきゃ。</t>
+          <t xml:space="preserve">何のために闘ってるのかしら…わからなくなったわ</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.seductive.normal[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5220,29 +5220,29 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高に痺れたわ。…また味わいたい、あの感覚</t>
+          <t xml:space="preserve">まだやれるわ…やってみせる</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.seductive.normal[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5252,29 +5252,29 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この輝き、よく似合うでしょう？ 欲しいなら…奪いに来なさい</t>
+          <t xml:space="preserve">やっと…戻ってこれたわ</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.seductive.normal[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5284,29 +5284,29 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.seductive.normal[1]</t>
+          <t xml:space="preserve">defeat.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">素敵な花道を用意してくれるのね。…ありがとう。最高の舞台だったわ</t>
+          <t xml:space="preserve">あの負けから…何かがおかしいの</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.seductive.normal[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5316,29 +5316,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.seductive.normal[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、私の魅力が伝わったかしら</t>
+          <t xml:space="preserve">体は治ったはずなのに…ね、動けないの</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.seductive.normal[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5348,29 +5348,29 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.seductive.normal[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一年間ずっと見ていてくれたでしょう？ …ちゃんと応えたわ</t>
+          <t xml:space="preserve">戻ってこれたのに…怖いの</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.seductive.normal[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5380,29 +5380,29 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.seductive.normal[1]</t>
+          <t xml:space="preserve">penalty_end.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">覚えておいて。この名前、来年はもっと大きなところで呼ばれるから</t>
+          <t xml:space="preserve">怪我は治ったのに…気力が戻らないの</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.springTagChampion.seductive.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">springTagChampion.seductive.normal[1]</t>
+          <t xml:space="preserve">autumnWarChampion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5427,14 +5427,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふたりで掴んだ春の主役の座、悪くない気分でしょう？</t>
+          <t xml:space="preserve">団体の名を背負うなら、このくらい華やかに勝たなきゃ。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">bestMatch.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5459,14 +5459,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふっ、いよいよドームね</t>
+          <t xml:space="preserve">最高に痺れたわ。…また味わいたい、あの感覚</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.normal[2]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[2]</t>
+          <t xml:space="preserve">champion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5491,14 +5491,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この大舞台で…見せたいものがあるの</t>
+          <t xml:space="preserve">この輝き、よく似合うでしょう？ 欲しいなら…奪いに来なさい</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.normal[3]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5508,12 +5508,12 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[3]</t>
+          <t xml:space="preserve">hallOfFame.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5523,14 +5523,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドームのお客様を…虜にしてあげる</t>
+          <t xml:space="preserve">素敵な花道を用意してくれるのね。…ありがとう。最高の舞台だったわ</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">mediaAward.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5555,14 +5555,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員のお客様…今夜の私に、酔いしれてくれたのね</t>
+          <t xml:space="preserve">ふふ、私の魅力が伝わったかしら</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.normal[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[2]</t>
+          <t xml:space="preserve">mvp.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5587,14 +5587,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ…この達成感、格別ね</t>
+          <t xml:space="preserve">一年間ずっと見ていてくれたでしょう？ …ちゃんと応えたわ</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.normal[3]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5604,12 +5604,12 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[3]</t>
+          <t xml:space="preserve">rookie.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5619,14 +5619,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">忘れられない夜になったわ</t>
+          <t xml:space="preserve">覚えておいて。この名前、来年はもっと大きなところで呼ばれるから</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5636,29 +5636,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.seductive.normal[1]</t>
+          <t xml:space="preserve">springTagChampion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近、体が素直に動いてくれるの。嬉しいわ</t>
+          <t xml:space="preserve">ふたりで掴んだ春の主役の座、悪くない気分でしょう？</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.normal[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5668,29 +5668,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.seductive.normal[2]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習が楽しくなってきた気がする</t>
+          <t xml:space="preserve">ふふっ、いよいよドームね</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.seductive.normal[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5700,29 +5700,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい仲間に恵まれたわ。心強いの</t>
+          <t xml:space="preserve">この大舞台で…見せたいものがあるの</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.seductive.normal[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.normal[3]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5732,29 +5732,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[3]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少し疲れただけよ。心配しないで</t>
+          <t xml:space="preserve">ドームのお客様を…虜にしてあげる</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.seductive.normal[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5764,29 +5764,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなに応援してもらえるなんて…嬉しいわ</t>
+          <t xml:space="preserve">満員のお客様…今夜の私に、酔いしれてくれたのね</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.seductive.normal[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5796,29 +5796,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もういいわ。分かったから</t>
+          <t xml:space="preserve">うふふ…この達成感、格別ね</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.seductive.normal[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.normal[3]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5828,29 +5828,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[3]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい、ちょっと考え事してて</t>
+          <t xml:space="preserve">忘れられない夜になったわ</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.seductive.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5860,29 +5860,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.seductive.normal[1]</t>
+          <t xml:space="preserve">N1.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら……ずいぶん安く見られたものね</t>
+          <t xml:space="preserve">最近、体が素直に動いてくれるの。嬉しいわ</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.seductive.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5892,29 +5892,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.seductive.normal[1]</t>
+          <t xml:space="preserve">N1.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、嬉しい。ありがとう</t>
+          <t xml:space="preserve">練習が楽しくなってきた気がする</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.seductive.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5924,29 +5924,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.seductive.normal[1]</t>
+          <t xml:space="preserve">N2.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合宿ね。しっかり鍛えるわ</t>
+          <t xml:space="preserve">いい仲間に恵まれたわ。心強いの</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.seductive.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5956,29 +5956,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.seductive.normal[1]</t>
+          <t xml:space="preserve">N3.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと見てくれてたのね…嬉しい。頑張るわ</t>
+          <t xml:space="preserve">少し疲れただけよ。心配しないで</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.seductive.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5988,29 +5988,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.seductive.normal[1]</t>
+          <t xml:space="preserve">N4.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。もう少し、頑張ってみるわ</t>
+          <t xml:space="preserve">こんなに応援してもらえるなんて…嬉しいわ</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.seductive.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6020,29 +6020,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.seductive.normal[1]</t>
+          <t xml:space="preserve">N5_low.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">メディア出演…？ 楽しみだわ</t>
+          <t xml:space="preserve">…もういいわ。分かったから</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.seductive.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6052,29 +6052,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.seductive.normal[1]</t>
+          <t xml:space="preserve">N5_warning.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しかったわ。こういう時間もいいわね</t>
+          <t xml:space="preserve">…ごめんなさい、ちょっと考え事してて</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.seductive.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.seductive.normal[1]</t>
+          <t xml:space="preserve">bonus_insult.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6099,14 +6099,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう。リフレッシュしてくるわね</t>
+          <t xml:space="preserve">あら……ずいぶん安く見られたものね</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.seductive.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.seductive.normal[1]</t>
+          <t xml:space="preserve">bonus.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6131,14 +6131,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう。早く戻れるように頑張るわ</t>
+          <t xml:space="preserve">あら、嬉しい。ありがとう</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.seductive.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.seductive.normal[1]</t>
+          <t xml:space="preserve">camp.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6163,14 +6163,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">しっかり吸収させてもらうわね</t>
+          <t xml:space="preserve">合宿ね。しっかり鍛えるわ</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.seductive.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.seductive.normal[1]</t>
+          <t xml:space="preserve">encourage_high_trust.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6195,14 +6195,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">メディア出演のお話？ 楽しみだわ</t>
+          <t xml:space="preserve">ずっと見てくれてたのね…嬉しい。頑張るわ</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.seductive.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E4.seductive.normal[1]</t>
+          <t xml:space="preserve">encourage.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6227,14 +6227,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新しいスカウトのお話が来てるみたいよ</t>
+          <t xml:space="preserve">…ありがとう。もう少し、頑張ってみるわ</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.seductive.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.seductive.normal[1]</t>
+          <t xml:space="preserve">media.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6259,14 +6259,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">他の団体からお誘いが来てるの</t>
+          <t xml:space="preserve">メディア出演…？ 楽しみだわ</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.seductive.normal[1]</t>
+          <t xml:space="preserve">party.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6291,14 +6291,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさいね…今日はちょっと、気持ちが入らなくて</t>
+          <t xml:space="preserve">楽しかったわ。こういう時間もいいわね</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.seductive.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.seductive.normal[1]</t>
+          <t xml:space="preserve">refresh_leave.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6323,14 +6323,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（「最近、ここにいる意味あるのかしら」と同僚に漏らしている）</t>
+          <t xml:space="preserve">ありがとう。リフレッシュしてくるわね</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.seductive.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.seductive.normal[1]</t>
+          <t xml:space="preserve">special_treatment.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6355,14 +6355,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「次のステージが待っているかも」と匂わせ投稿）</t>
+          <t xml:space="preserve">ありがとう。早く戻れるように頑張るわ</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.seductive.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6372,12 +6372,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.seductive.normal[1]</t>
+          <t xml:space="preserve">trainer.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6387,14 +6387,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">タイトルマッチの機会、いただけないかしら</t>
+          <t xml:space="preserve">しっかり吸収させてもらうわね</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.seductive.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.seductive.normal[1]</t>
+          <t xml:space="preserve">E1.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6419,14 +6419,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人との試合、組んでもらえないかしら</t>
+          <t xml:space="preserve">メディア出演のお話？ 楽しみだわ</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.seductive.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.seductive.normal[1]</t>
+          <t xml:space="preserve">E4.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6451,14 +6451,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少し休ませてもらえないかしら…</t>
+          <t xml:space="preserve">新しいスカウトのお話が来てるみたいよ</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.seductive.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.seductive.normal[1]</t>
+          <t xml:space="preserve">E6.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6483,14 +6483,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このままじゃ困るわ。ちゃんと考えてもらえないかしら</t>
+          <t xml:space="preserve">他の団体からお誘いが来てるの</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.seductive.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.seductive.normal[1]</t>
+          <t xml:space="preserve">S_boycott.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6515,14 +6515,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…（沈黙）…ううん、なんでもないの</t>
+          <t xml:space="preserve">ごめんなさいね…今日はちょっと、気持ちが入らなくて</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.seductive.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.seductive.normal[1]</t>
+          <t xml:space="preserve">S_grumble.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6547,14 +6547,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">特訓させてもらえないかしら？</t>
+          <t xml:space="preserve">（「最近、ここにいる意味あるのかしら」と同僚に漏らしている）</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.seductive.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.seductive.normal[1]</t>
+          <t xml:space="preserve">S_sns.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6579,14 +6579,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の指導、私にやらせてもらえないかしら</t>
+          <t xml:space="preserve">（SNSに「次のステージが待っているかも」と匂わせ投稿）</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.seductive.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.seductive.normal[1]</t>
+          <t xml:space="preserve">S1.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6611,14 +6611,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し時間がかかりそう。ごめんなさいね</t>
+          <t xml:space="preserve">タイトルマッチの機会、いただけないかしら</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.seductive.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6628,12 +6628,12 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.seductive.normal[1]</t>
+          <t xml:space="preserve">S2.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6643,14 +6643,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人とはもう無理よ。何とかしてもらえないかしら</t>
+          <t xml:space="preserve">あの人との試合、組んでもらえないかしら</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.seductive.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.seductive.normal[1]</t>
+          <t xml:space="preserve">S3.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6675,14 +6675,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">向こうにも非があるのに…私だけが悪いの？</t>
+          <t xml:space="preserve">少し休ませてもらえないかしら…</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.seductive.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.seductive.normal[1]</t>
+          <t xml:space="preserve">S4_direct.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6707,14 +6707,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私のイメージに合うブランドね。いい選択だわ♡</t>
+          <t xml:space="preserve">このままじゃ困るわ。ちゃんと考えてもらえないかしら</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.seductive.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.seductive.normal[1]</t>
+          <t xml:space="preserve">S4_silent.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6739,14 +6739,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">カメラの前ね…いい絵、撮らせてあげる♡</t>
+          <t xml:space="preserve">…（沈黙）…ううん、なんでもないの</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.seductive.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6756,12 +6756,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.seductive.normal[1]</t>
+          <t xml:space="preserve">S5.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6771,14 +6771,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンと直接会える機会ね…喜ばせてあげるわ♡</t>
+          <t xml:space="preserve">特訓させてもらえないかしら？</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.seductive.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6788,12 +6788,12 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.seductive.normal[1]</t>
+          <t xml:space="preserve">S6.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6803,14 +6803,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ランウェイか…私の本領発揮ね♡</t>
+          <t xml:space="preserve">後輩の指導、私にやらせてもらえないかしら</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.seductive.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.seductive.normal[1]</t>
+          <t xml:space="preserve">B1.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6835,14 +6835,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">グラビアね…全部見せてあげるわ♡</t>
+          <t xml:space="preserve">…少し時間がかかりそう。ごめんなさいね</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.seductive.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.seductive.normal[1]</t>
+          <t xml:space="preserve">B2_fighter1.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6867,14 +6867,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バラエティねぇ。じゃあ、素の私を少し見せてあげようかしら</t>
+          <t xml:space="preserve">あの人とはもう無理よ。何とかしてもらえないかしら</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.seductive.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.seductive.normal[1]</t>
+          <t xml:space="preserve">B2_fighter2.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6899,14 +6899,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">取材ね…いい姿を見せてあげるわ</t>
+          <t xml:space="preserve">向こうにも非があるのに…私だけが悪いの？</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6916,29 +6916,29 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">B4_brand.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでくれるなら…期待に応えるわよ</t>
+          <t xml:space="preserve">私のイメージに合うブランドね。いい選択だわ♡</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6948,29 +6948,29 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">B4_cm.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくね。期待に応えてあげる</t>
+          <t xml:space="preserve">カメラの前ね…いい絵、撮らせてあげる♡</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.normal[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6980,29 +6980,29 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[2]</t>
+          <t xml:space="preserve">B4_fan.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、選んでくれてありがとう</t>
+          <t xml:space="preserve">ファンと直接会える機会ね…喜ばせてあげるわ♡</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7012,29 +7012,29 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">B4_fashion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくね。力になるわ</t>
+          <t xml:space="preserve">ランウェイか…私の本領発揮ね♡</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7044,29 +7044,29 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">B4_gravure.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくね。精一杯やるわ</t>
+          <t xml:space="preserve">グラビアね…全部見せてあげるわ♡</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7076,29 +7076,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">B4_variety.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ちょっとだけ、休ませてね</t>
+          <t xml:space="preserve">バラエティねぇ。じゃあ、素の私を少し見せてあげようかしら</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.normal[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7108,29 +7108,29 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[2]</t>
+          <t xml:space="preserve">B4.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すぐに戻るわ。待っててくれる？</t>
+          <t xml:space="preserve">取材ね…いい姿を見せてあげるわ</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7162,7 +7162,7 @@
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7194,7 +7194,7 @@
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.normal[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7204,12 +7204,12 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.seductive.normal[2]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7226,7 +7226,7 @@
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7236,12 +7236,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7251,14 +7251,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わざわざ口説きに来るなんて。…物好きね、あなた。</t>
+          <t xml:space="preserve">よろしくね。力になるわ</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7283,14 +7283,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくね。力になるわ</t>
+          <t xml:space="preserve">よろしくね。精一杯やるわ</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7315,14 +7315,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくね。精一杯やるわ</t>
+          <t xml:space="preserve">…ちょっとだけ、休ませてね</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7332,12 +7332,12 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7347,14 +7347,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ちょっとだけ、休ませてね</t>
+          <t xml:space="preserve">すぐに戻るわ。待っててくれる？</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.seductive.normal[2]</t>
+          <t xml:space="preserve">draftInterest.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7379,14 +7379,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すぐに戻るわ。待っててくれる？</t>
+          <t xml:space="preserve">選んでくれるなら…期待に応えるわよ</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.seductive.normal[1]</t>
+          <t xml:space="preserve">draftJoin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7411,14 +7411,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここでの思い出、大切にするわ</t>
+          <t xml:space="preserve">よろしくね。期待に応えてあげる</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.seductive.normal[2]</t>
+          <t xml:space="preserve">draftJoin.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7443,14 +7443,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お世話になりました。また、どこかで</t>
+          <t xml:space="preserve">ふふ、選んでくれてありがとう</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.seductive.normal[1]</t>
+          <t xml:space="preserve">faGreeting.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7475,14 +7475,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間だけど、よろしくね</t>
+          <t xml:space="preserve">わざわざ口説きに来るなんて。…物好きね、あなた。</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.seductive.normal[1]</t>
+          <t xml:space="preserve">faSigning.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7507,14 +7507,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">目をつけたのはそっち。…責任、取ってね</t>
+          <t xml:space="preserve">よろしくね。力になるわ</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.seductive.normal[1]</t>
+          <t xml:space="preserve">faWelcome.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7539,14 +7539,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいわ…でも、次こそはね</t>
+          <t xml:space="preserve">よろしくね。精一杯やるわ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.seductive.normal[1]</t>
+          <t xml:space="preserve">injury.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7571,14 +7571,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛成功…。このベルト、まだ返す気はないわ</t>
+          <t xml:space="preserve">…ちょっとだけ、休ませてね</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.seductive.normal[1]</t>
+          <t xml:space="preserve">injury.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7603,14 +7603,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトがない景色なんて…でも、ここで終わらないわ</t>
+          <t xml:space="preserve">すぐに戻るわ。待っててくれる？</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.seductive.normal[1]</t>
+          <t xml:space="preserve">release.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7635,14 +7635,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオン…最高の気分ね</t>
+          <t xml:space="preserve">ここでの思い出、大切にするわ</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">release.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7667,14 +7667,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここでの思い出、大切にするわ</t>
+          <t xml:space="preserve">お世話になりました。また、どこかで</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7684,12 +7684,12 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[2]</t>
+          <t xml:space="preserve">rentalGreeting.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7699,14 +7699,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お世話になりました。また、どこかで</t>
+          <t xml:space="preserve">短い間だけど、よろしくね</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">scoutGreeting.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7731,14 +7731,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間だけど、よろしくね</t>
+          <t xml:space="preserve">目をつけたのはそっち。…責任、取ってね</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7770,7 +7770,7 @@
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7780,12 +7780,12 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">titleDefense.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7802,7 +7802,7 @@
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7812,12 +7812,12 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">titleLoss.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7834,7 +7834,7 @@
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">titleWin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7866,7 +7866,7 @@
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7876,29 +7876,29 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう…合わないみたいね</t>
+          <t xml:space="preserve">ここでの思い出、大切にするわ</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7908,29 +7908,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近どこか冷たいわ…気のせいかしら</t>
+          <t xml:space="preserve">お世話になりました。また、どこかで</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7940,29 +7940,29 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なかなか面白い人ね。もっと近くで見ていたい</t>
+          <t xml:space="preserve">短い間だけど、よろしくね</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7972,29 +7972,29 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">特別な存在。他の誰とも違うの</t>
+          <t xml:space="preserve">悔しいわ…でも、次こそはね</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8004,29 +8004,29 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もういいかしら。次を探さなきゃ</t>
+          <t xml:space="preserve">防衛成功…。このベルト、まだ返す気はないわ</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8036,29 +8036,29 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気になるわ…潰しがいがありそうね</t>
+          <t xml:space="preserve">ベルトがない景色なんて…でも、ここで終わらないわ</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8068,29 +8068,29 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.normal.seductive[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうしても許せない。必ず私が勝つわ</t>
+          <t xml:space="preserve">チャンピオン…最高の気分ね</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.normal.seductive[1]</t>
+          <t xml:space="preserve">bond_39_down.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8115,14 +8115,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私の全て…最高の獲物よ</t>
+          <t xml:space="preserve">もう…合わないみたいね</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.normal.seductive[1]</t>
+          <t xml:space="preserve">bond_59_down.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8147,14 +8147,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここでなら…私らしくいられるわ</t>
+          <t xml:space="preserve">最近どこか冷たいわ…気のせいかしら</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.normal.seductive[1]</t>
+          <t xml:space="preserve">bond_60_up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8179,14 +8179,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここにはもう何も残ってないわ</t>
+          <t xml:space="preserve">なかなか面白い人ね。もっと近くで見ていたい</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.normal.seductive[1]</t>
+          <t xml:space="preserve">bond_80_up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8211,14 +8211,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここにいる意味…本当にあるのかしら</t>
+          <t xml:space="preserve">特別な存在。他の誰とも違うの</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.seductive.normal[1]</t>
+          <t xml:space="preserve">rivalry_29_down.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8243,14 +8243,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けは負け。でも…悪くない戦いだったわ</t>
+          <t xml:space="preserve">もういいかしら。次を探さなきゃ</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.seductive.normal[1]</t>
+          <t xml:space="preserve">rivalry_30_up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8275,14 +8275,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">完璧な夜ね…最高の気分だわ</t>
+          <t xml:space="preserve">気になるわ…潰しがいがありそうね</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.seductive.normal[1]</t>
+          <t xml:space="preserve">rivalry_50_up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8307,14 +8307,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたのね…屈辱だわ</t>
+          <t xml:space="preserve">どうしても許せない。必ず私が勝つわ</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.seductive.normal[1]</t>
+          <t xml:space="preserve">rivalry_70_up.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8339,14 +8339,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、今日も勝ち。気分がいいわ</t>
+          <t xml:space="preserve">私の全て…最高の獲物よ</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8356,12 +8356,12 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.seductive.normal[1]</t>
+          <t xml:space="preserve">trust_above_75.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8371,14 +8371,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">汗を流すのも悪くないわね</t>
+          <t xml:space="preserve">ここでなら…私らしくいられるわ</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.seductive.normal[1]</t>
+          <t xml:space="preserve">trust_below_20.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8403,14 +8403,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ねぇ…最近私のこと放置してない？</t>
+          <t xml:space="preserve">ここにはもう何も残ってないわ</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.seductive[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.seductive.normal[1]</t>
+          <t xml:space="preserve">trust_below_35.normal.seductive[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8435,14 +8435,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近いい扱い受けてる気がするわ。嬉しいわね</t>
+          <t xml:space="preserve">ここにいる意味…本当にあるのかしら</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8467,14 +8467,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと気になってるの。いい距離感よね</t>
+          <t xml:space="preserve">負けは負け。でも…悪くない戦いだったわ</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8499,14 +8499,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…考えちゃうのよね</t>
+          <t xml:space="preserve">完璧な夜ね…最高の気分だわ</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-01.loss.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8531,14 +8531,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を干すつもり？ もったいないと思うけど</t>
+          <t xml:space="preserve">負けたのね…屈辱だわ</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-01.win.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8563,14 +8563,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体が言うこと聞かないわ…もどかしい</t>
+          <t xml:space="preserve">ふふ、今日も勝ち。気分がいいわ</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-02.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8595,14 +8595,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負け続き…こんなの私じゃないわ</t>
+          <t xml:space="preserve">汗を流すのも悪くないわね</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8617,7 +8617,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-03.down.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8627,14 +8627,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近負けなしよ。ふふ、誰が相手でも返り討ちだわ</t>
+          <t xml:space="preserve">ねぇ…最近私のこと放置してない？</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-03.up.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8659,14 +8659,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">退屈…早くリングに立ちたいわ</t>
+          <t xml:space="preserve">最近いい扱い受けてる気がするわ。嬉しいわね</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-04.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8691,14 +8691,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いたわね、そういえば。……それだけよ</t>
+          <t xml:space="preserve">ちょっと気になってるの。いい距離感よね</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">GL-05.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8723,14 +8723,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、いつもの私に戻ったみたい。でも悪くない気分よ</t>
+          <t xml:space="preserve">…考えちゃうのよね</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8740,29 +8740,29 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-06.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体、まだ震えてるの。でも…この傷ごと、最後の舞台に上がるわ</t>
+          <t xml:space="preserve">私を干すつもり？ もったいないと思うけど</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8772,29 +8772,29 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.normal[2]</t>
+          <t xml:space="preserve">GL-07.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぼろぼろでしょ、私。でもね…一番きれいに終わらせるのは、こういう時よ</t>
+          <t xml:space="preserve">体が言うこと聞かないわ…もどかしい</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8804,29 +8804,29 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-08.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">来るなら誰でもいいわ。全部、受け止めてあげる</t>
+          <t xml:space="preserve">負け続き…こんなの私じゃないわ</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8836,29 +8836,29 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.normal[2]</t>
+          <t xml:space="preserve">GL-09.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この一戦、たっぷり付き合ってもらうわよ。逃がさないから</t>
+          <t xml:space="preserve">最近負けなしよ。ふふ、誰が相手でも返り討ちだわ</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8868,29 +8868,29 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-10.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、落としたわ。…息、荒いでしょ？ でも、まだ物足りないの。次、出してよ</t>
+          <t xml:space="preserve">退屈…早くリングに立ちたいわ</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8900,29 +8900,29 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.normal[2]</t>
+          <t xml:space="preserve">GL-11.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってるの。次の子、早くいらっしゃい。ここは、渡さないから</t>
+          <t xml:space="preserve">いたわね、そういえば。……それだけよ</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8932,29 +8932,29 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で勝ったのよ。この勝利は、一人じゃ味わえない特別なもの</t>
+          <t xml:space="preserve">あら、いつもの私に戻ったみたい。でも悪くない気分よ</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.normal[2]</t>
+          <t xml:space="preserve">preFinal.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8979,14 +8979,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が繋いでくれた……その信頼に応えられたなら、嬉しいわ</t>
+          <t xml:space="preserve">身体、まだ震えてるの。でも…この傷ごと、最後の舞台に上がるわ</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.normal[1]</t>
+          <t xml:space="preserve">preFinal.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9011,14 +9011,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">個人賞……嬉しくないとは言わない。でも、欲しかったのはこれじゃないの</t>
+          <t xml:space="preserve">ぼろぼろでしょ、私。でもね…一番きれいに終わらせるのは、こういう時よ</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.normal[2]</t>
+          <t xml:space="preserve">preMatch.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9043,14 +9043,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次は団体ごと勝つわ。そうでなきゃ……意味がないもの</t>
+          <t xml:space="preserve">来るなら誰でもいいわ。全部、受け止めてあげる</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9060,12 +9060,12 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.normal[1]</t>
+          <t xml:space="preserve">preMatch.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9075,14 +9075,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ震えてるの、身体。でもね、この汗と痛みが……今日の私を証明してくれてる</t>
+          <t xml:space="preserve">この一戦、たっぷり付き合ってもらうわよ。逃がさないから</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.normal[2]</t>
+          <t xml:space="preserve">survivor.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9107,14 +9107,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">倒しても倒しても来るの。でも、最後に立ってたのはこっち。悪くないでしょ？</t>
+          <t xml:space="preserve">一人、落としたわ。…息、荒いでしょ？ でも、まだ物足りないの。次、出してよ</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9124,12 +9124,12 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.normal[1]</t>
+          <t xml:space="preserve">survivor.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9139,14 +9139,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝。…最高の気分ね</t>
+          <t xml:space="preserve">まだ立ってるの。次の子、早くいらっしゃい。ここは、渡さないから</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9156,12 +9156,12 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.normal[2]</t>
+          <t xml:space="preserve">champion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9171,14 +9171,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、これで終わりじゃないわよ</t>
+          <t xml:space="preserve">三人で勝ったのよ。この勝利は、一人じゃ味わえない特別なもの</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9188,12 +9188,12 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.seductive.normal[1]</t>
+          <t xml:space="preserve">champion.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9203,14 +9203,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、残念ね。でも次があるわ</t>
+          <t xml:space="preserve">仲間が繋いでくれた……その信頼に応えられたなら、嬉しいわ</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.seductive.normal[2]</t>
+          <t xml:space="preserve">defiant.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9235,14 +9235,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいけど…いい経験だったわ</t>
+          <t xml:space="preserve">個人賞……嬉しくないとは言わない。でも、欲しかったのはこれじゃないの</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9252,12 +9252,12 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.seductive.normal[1]</t>
+          <t xml:space="preserve">defiant.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9267,14 +9267,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、まずは一勝ね。次も魅せてあげるわ</t>
+          <t xml:space="preserve">次は団体ごと勝つわ。そうでなきゃ……意味がないもの</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9284,12 +9284,12 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.seductive.normal[2]</t>
+          <t xml:space="preserve">gauntlet.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9299,14 +9299,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てたわ。……でもまだ先がある</t>
+          <t xml:space="preserve">まだ震えてるの、身体。でもね、この汗と痛みが……今日の私を証明してくれてる</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9316,12 +9316,12 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.seductive.normal[1]</t>
+          <t xml:space="preserve">gauntlet.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9331,14 +9331,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい経験だったわ。もっと魅せられるようになりたいわね</t>
+          <t xml:space="preserve">倒しても倒しても来るの。でも、最後に立ってたのはこっち。悪くないでしょ？</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.seductive.normal[2]</t>
+          <t xml:space="preserve">champion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9363,14 +9363,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだこんなものじゃないわよ</t>
+          <t xml:space="preserve">優勝。…最高の気分ね</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.normal[1]</t>
+          <t xml:space="preserve">champion.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9395,14 +9395,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝…。最後の舞台、最高に魅せてあげるわ</t>
+          <t xml:space="preserve">ふふ、これで終わりじゃないわよ</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.normal[2]</t>
+          <t xml:space="preserve">postLose.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9427,14 +9427,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あと一つ。全てを懸けるわ</t>
+          <t xml:space="preserve">あら、残念ね。でも次があるわ</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.normal[1]</t>
+          <t xml:space="preserve">postLose.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9459,14 +9459,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次の相手…楽しみね</t>
+          <t xml:space="preserve">悔しいけど…いい経験だったわ</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9481,7 +9481,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.normal[2]</t>
+          <t xml:space="preserve">postMatchWin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9491,14 +9491,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私の魅力、見せつけてあげる</t>
+          <t xml:space="preserve">ふふ、まずは一勝ね。次も魅せてあげるわ</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.seductive.normal[1]</t>
+          <t xml:space="preserve">postMatchWin.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9523,14 +9523,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">出場が決まったわ。見ていてね</t>
+          <t xml:space="preserve">勝てたわ。……でもまだ先がある</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.seductive.normal[2]</t>
+          <t xml:space="preserve">postWin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9555,14 +9555,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">素敵な舞台ね。魅せてあげるわ</t>
+          <t xml:space="preserve">いい経験だったわ。もっと魅せられるようになりたいわね</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">postWin.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9587,14 +9587,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は負けるわけにはいかないの。覚悟してね</t>
+          <t xml:space="preserve">まだまだこんなものじゃないわよ</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9604,12 +9604,12 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">preFinal.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9619,14 +9619,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ……最高の舞台で、最高の結末。悪くないわね</t>
+          <t xml:space="preserve">決勝…。最後の舞台、最高に魅せてあげるわ</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9636,12 +9636,12 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[2]</t>
+          <t xml:space="preserve">preFinal.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9651,14 +9651,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見ててくれた？ これが私のすべてよ</t>
+          <t xml:space="preserve">あと一つ。全てを懸けるわ</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">preMatch.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9683,14 +9683,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ、おたくの団体さん…少し気になってたの</t>
+          <t xml:space="preserve">次の相手…楽しみね</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9700,12 +9700,12 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[2]</t>
+          <t xml:space="preserve">preMatch.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9715,14 +9715,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">遊んであげるわ。……本気でね</t>
+          <t xml:space="preserve">私の魅力、見せつけてあげる</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9732,12 +9732,12 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">summon.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9747,14 +9747,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら…怖いのかしら。可哀想</t>
+          <t xml:space="preserve">出場が決まったわ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9764,12 +9764,12 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[2]</t>
+          <t xml:space="preserve">summon.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9779,14 +9779,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃げるのね…。つまらないわ</t>
+          <t xml:space="preserve">素敵な舞台ね。魅せてあげるわ</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.normal[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9811,14 +9811,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃったわね…悔しい</t>
+          <t xml:space="preserve">今日は負けるわけにはいかないの。覚悟してね</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.normal[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.seductive.normal[2]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9843,14 +9843,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次はもっと綺麗に勝ってみせるわ</t>
+          <t xml:space="preserve">ふふ……最高の舞台で、最高の結末。悪くないわね</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.normal[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9860,12 +9860,12 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9875,14 +9875,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、勝てたわね。素敵な対抗戦だったわ</t>
+          <t xml:space="preserve">見ててくれた？ これが私のすべてよ</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.normal[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9892,12 +9892,12 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.seductive.normal[2]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9907,14 +9907,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝利の味は…格別ね</t>
+          <t xml:space="preserve">うふふ、おたくの団体さん…少し気になってたの</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9924,12 +9924,12 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9939,14 +9939,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、もう終わり？ 物足りなかったわ</t>
+          <t xml:space="preserve">遊んであげるわ。……本気でね</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.normal[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9956,12 +9956,12 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[2]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9971,14 +9971,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うちの団体の底力、見せてあげたわよ</t>
+          <t xml:space="preserve">あら…怖いのかしら。可哀想</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.normal[3]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9988,12 +9988,12 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[3]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10003,14 +10003,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、うちの団体の魅力、わかっていただけたかしら</t>
+          <t xml:space="preserve">逃げるのね…。つまらないわ</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.seductive.normal[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10020,29 +10020,29 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.seductive.normal[1]</t>
+          <t xml:space="preserve">result_lose.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来れたのね…最高の気分だわ</t>
+          <t xml:space="preserve">負けちゃったわね…悔しい</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10052,59 +10052,283 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">result_lose.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わざわざ口説きに来るなんて。…物好きね、あなた。</t>
+          <t xml:space="preserve">次はもっと綺麗に勝ってみせるわ</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.normal[1]</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.seductive.normal[1]</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふふ、勝てたわね。素敵な対抗戦だったわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="40" customHeight="1">
+      <c r="A307" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.normal[2]</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.seductive.normal[2]</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝利の味は…格別ね</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="40" customHeight="1">
+      <c r="A308" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.normal[1]</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.normal[1]</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、もう終わり？ 物足りなかったわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="40" customHeight="1">
+      <c r="A309" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.normal[2]</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.normal[2]</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">うちの団体の底力、見せてあげたわよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="40" customHeight="1">
+      <c r="A310" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.normal[3]</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.normal[3]</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふふ、うちの団体の魅力、わかっていただけたかしら</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="40" customHeight="1">
+      <c r="A311" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.seductive.normal[1]</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.seductive.normal[1]</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここまで来れたのね…最高の気分だわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="40" customHeight="1">
+      <c r="A312" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.seductive.normal[1]</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.normal[1]</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わざわざ口説きに来るなんて。…物好きね、あなた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="40" customHeight="1">
+      <c r="A313" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.seductive.normal[1]</t>
         </is>
       </c>
-      <c r="B306" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr" s="2">
+      <c r="B313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr" s="12">
+      <c r="D313" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
-      <c r="E306" t="inlineStr" s="2">
+      <c r="E313" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F306" t="inlineStr" s="3">
+      <c r="F313" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">目をつけたのはそっち。…責任、取ってね</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H306"/>
+  <autoFilter ref="A1:H313"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/蠱惑×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×ノーマル.xlsx
@@ -284,7 +284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H306"/>
+  <dimension ref="A1:H307"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -8346,7 +8346,7 @@
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02-hostile.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-02-hostile.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8371,14 +8371,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">汗を流すのも悪くないわね</t>
+          <t xml:space="preserve">…あら、また考えてしまった。ま、それが原動力になるなら悪くないけど</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-02.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8403,14 +8403,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ねぇ…最近私のこと放置してない？</t>
+          <t xml:space="preserve">汗を流すのも悪くないわね</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-03.down.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8435,14 +8435,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近いい扱い受けてる気がするわ。嬉しいわね</t>
+          <t xml:space="preserve">ねぇ…最近私のこと放置してない？</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-03.up.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8467,14 +8467,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと気になってるの。いい距離感よね</t>
+          <t xml:space="preserve">最近いい扱い受けてる気がするわ。嬉しいわね</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-04.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8499,14 +8499,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…考えちゃうのよね</t>
+          <t xml:space="preserve">ちょっと気になってるの。いい距離感よね</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-05.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8531,14 +8531,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を干すつもり？ もったいないと思うけど</t>
+          <t xml:space="preserve">…考えちゃうのよね</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-06.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8563,14 +8563,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体が言うこと聞かないわ…もどかしい</t>
+          <t xml:space="preserve">私を干すつもり？ もったいないと思うけど</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-07.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8595,14 +8595,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負け続き…こんなの私じゃないわ</t>
+          <t xml:space="preserve">体が言うこと聞かないわ…もどかしい</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8617,7 +8617,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-08.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8627,14 +8627,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近負けなしよ。ふふ、誰が相手でも返り討ちだわ</t>
+          <t xml:space="preserve">負け続き…こんなの私じゃないわ</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-09.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8659,14 +8659,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">退屈…早くリングに立ちたいわ</t>
+          <t xml:space="preserve">最近負けなしよ。ふふ、誰が相手でも返り討ちだわ</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.seductive.normal[1]</t>
+          <t xml:space="preserve">GL-10.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8691,14 +8691,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いたわね、そういえば。……それだけよ</t>
+          <t xml:space="preserve">退屈…早くリングに立ちたいわ</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">GL-11.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8723,14 +8723,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、いつもの私に戻ったみたい。でも悪くない気分よ</t>
+          <t xml:space="preserve">いたわね、そういえば。……それだけよ</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8740,29 +8740,29 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体、まだ震えてるの。でも…この傷ごと、最後の舞台に上がるわ</t>
+          <t xml:space="preserve">あら、いつもの私に戻ったみたい。でも悪くない気分よ</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.normal[2]</t>
+          <t xml:space="preserve">preFinal.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8787,14 +8787,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぼろぼろでしょ、私。でもね…一番きれいに終わらせるのは、こういう時よ</t>
+          <t xml:space="preserve">身体、まだ震えてるの。でも…この傷ごと、最後の舞台に上がるわ</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8809,7 +8809,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.normal[1]</t>
+          <t xml:space="preserve">preFinal.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8819,14 +8819,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">来るなら誰でもいいわ。全部、受け止めてあげる</t>
+          <t xml:space="preserve">ぼろぼろでしょ、私。でもね…一番きれいに終わらせるのは、こういう時よ</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.normal[2]</t>
+          <t xml:space="preserve">preMatch.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8851,14 +8851,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この一戦、たっぷり付き合ってもらうわよ。逃がさないから</t>
+          <t xml:space="preserve">来るなら誰でもいいわ。全部、受け止めてあげる</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8873,7 +8873,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.normal[1]</t>
+          <t xml:space="preserve">preMatch.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8883,14 +8883,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、落としたわ。…息、荒いでしょ？ でも、まだ物足りないの。次、出してよ</t>
+          <t xml:space="preserve">この一戦、たっぷり付き合ってもらうわよ。逃がさないから</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.normal[2]</t>
+          <t xml:space="preserve">survivor.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8915,14 +8915,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってるの。次の子、早くいらっしゃい。ここは、渡さないから</t>
+          <t xml:space="preserve">一人、落としたわ。…息、荒いでしょ？ でも、まだ物足りないの。次、出してよ</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.normal[1]</t>
+          <t xml:space="preserve">survivor.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8947,14 +8947,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で勝ったのよ。この勝利は、一人じゃ味わえない特別なもの</t>
+          <t xml:space="preserve">まだ立ってるの。次の子、早くいらっしゃい。ここは、渡さないから</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8969,7 +8969,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.normal[2]</t>
+          <t xml:space="preserve">champion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8979,14 +8979,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が繋いでくれた……その信頼に応えられたなら、嬉しいわ</t>
+          <t xml:space="preserve">三人で勝ったのよ。この勝利は、一人じゃ味わえない特別なもの</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.normal[1]</t>
+          <t xml:space="preserve">champion.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9011,14 +9011,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">個人賞……嬉しくないとは言わない。でも、欲しかったのはこれじゃないの</t>
+          <t xml:space="preserve">仲間が繋いでくれた……その信頼に応えられたなら、嬉しいわ</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.normal[2]</t>
+          <t xml:space="preserve">defiant.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9043,14 +9043,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次は団体ごと勝つわ。そうでなきゃ……意味がないもの</t>
+          <t xml:space="preserve">個人賞……嬉しくないとは言わない。でも、欲しかったのはこれじゃないの</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.normal[1]</t>
+          <t xml:space="preserve">defiant.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9075,14 +9075,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ震えてるの、身体。でもね、この汗と痛みが……今日の私を証明してくれてる</t>
+          <t xml:space="preserve">次は団体ごと勝つわ。そうでなきゃ……意味がないもの</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.normal[2]</t>
+          <t xml:space="preserve">gauntlet.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9107,14 +9107,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">倒しても倒しても来るの。でも、最後に立ってたのはこっち。悪くないでしょ？</t>
+          <t xml:space="preserve">まだ震えてるの、身体。でもね、この汗と痛みが……今日の私を証明してくれてる</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9124,12 +9124,12 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.normal[1]</t>
+          <t xml:space="preserve">gauntlet.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9139,14 +9139,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝。…最高の気分ね</t>
+          <t xml:space="preserve">倒しても倒しても来るの。でも、最後に立ってたのはこっち。悪くないでしょ？</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.normal[2]</t>
+          <t xml:space="preserve">champion.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9171,14 +9171,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、これで終わりじゃないわよ</t>
+          <t xml:space="preserve">優勝。…最高の気分ね</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9193,7 +9193,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.seductive.normal[1]</t>
+          <t xml:space="preserve">champion.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9203,14 +9203,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、残念ね。でも次があるわ</t>
+          <t xml:space="preserve">ふふ、これで終わりじゃないわよ</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.seductive.normal[2]</t>
+          <t xml:space="preserve">postLose.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9235,14 +9235,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいけど…いい経験だったわ</t>
+          <t xml:space="preserve">あら、残念ね。でも次があるわ</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.seductive.normal[1]</t>
+          <t xml:space="preserve">postLose.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9267,14 +9267,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、まずは一勝ね。次も魅せてあげるわ</t>
+          <t xml:space="preserve">悔しいけど…いい経験だったわ</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.seductive.normal[2]</t>
+          <t xml:space="preserve">postMatchWin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9299,14 +9299,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てたわ。……でもまだ先がある</t>
+          <t xml:space="preserve">ふふ、まずは一勝ね。次も魅せてあげるわ</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.seductive.normal[1]</t>
+          <t xml:space="preserve">postMatchWin.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9331,14 +9331,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい経験だったわ。もっと魅せられるようになりたいわね</t>
+          <t xml:space="preserve">勝てたわ。……でもまだ先がある</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.seductive.normal[2]</t>
+          <t xml:space="preserve">postWin.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9363,14 +9363,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだこんなものじゃないわよ</t>
+          <t xml:space="preserve">いい経験だったわ。もっと魅せられるようになりたいわね</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.normal[1]</t>
+          <t xml:space="preserve">postWin.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9395,14 +9395,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝…。最後の舞台、最高に魅せてあげるわ</t>
+          <t xml:space="preserve">まだまだこんなものじゃないわよ</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.normal[2]</t>
+          <t xml:space="preserve">preFinal.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9427,14 +9427,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あと一つ。全てを懸けるわ</t>
+          <t xml:space="preserve">決勝…。最後の舞台、最高に魅せてあげるわ</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.normal[1]</t>
+          <t xml:space="preserve">preFinal.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9459,14 +9459,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次の相手…楽しみね</t>
+          <t xml:space="preserve">あと一つ。全てを懸けるわ</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9481,7 +9481,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.normal[2]</t>
+          <t xml:space="preserve">preMatch.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9491,14 +9491,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私の魅力、見せつけてあげる</t>
+          <t xml:space="preserve">次の相手…楽しみね</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.seductive.normal[1]</t>
+          <t xml:space="preserve">preMatch.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9523,14 +9523,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">出場が決まったわ。見ていてね</t>
+          <t xml:space="preserve">私の魅力、見せつけてあげる</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.seductive.normal[2]</t>
+          <t xml:space="preserve">summon.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9555,14 +9555,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">素敵な舞台ね。魅せてあげるわ</t>
+          <t xml:space="preserve">出場が決まったわ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">summon.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9587,14 +9587,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は負けるわけにはいかないの。覚悟してね</t>
+          <t xml:space="preserve">素敵な舞台ね。魅せてあげるわ</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
@@ -9619,14 +9619,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ……最高の舞台で、最高の結末。悪くないわね</t>
+          <t xml:space="preserve">今日は負けるわけにはいかないの。覚悟してね</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.normal[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[2]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9651,14 +9651,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見ててくれた？ これが私のすべてよ</t>
+          <t xml:space="preserve">ふふ……最高の舞台で、最高の結末。悪くないわね</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.normal[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9683,14 +9683,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ、おたくの団体さん…少し気になってたの</t>
+          <t xml:space="preserve">見ててくれた？ これが私のすべてよ</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.normal[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[2]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9715,14 +9715,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">遊んであげるわ。……本気でね</t>
+          <t xml:space="preserve">うふふ、おたくの団体さん…少し気になってたの</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.normal[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9732,12 +9732,12 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9747,14 +9747,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら…怖いのかしら。可哀想</t>
+          <t xml:space="preserve">遊んであげるわ。……本気でね</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.normal[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[2]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9779,14 +9779,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃げるのね…。つまらないわ</t>
+          <t xml:space="preserve">あら…怖いのかしら。可哀想</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.normal[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9811,14 +9811,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃったわね…悔しい</t>
+          <t xml:space="preserve">逃げるのね…。つまらないわ</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.normal[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.seductive.normal[2]</t>
+          <t xml:space="preserve">result_lose.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9843,14 +9843,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次はもっと綺麗に勝ってみせるわ</t>
+          <t xml:space="preserve">負けちゃったわね…悔しい</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.normal[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.seductive.normal[1]</t>
+          <t xml:space="preserve">result_lose.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9875,14 +9875,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、勝てたわね。素敵な対抗戦だったわ</t>
+          <t xml:space="preserve">次はもっと綺麗に勝ってみせるわ</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.normal[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.seductive.normal[2]</t>
+          <t xml:space="preserve">result_win.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9907,14 +9907,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝利の味は…格別ね</t>
+          <t xml:space="preserve">ふふ、勝てたわね。素敵な対抗戦だったわ</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9924,12 +9924,12 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">result_win.seductive.normal[2]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9939,14 +9939,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、もう終わり？ 物足りなかったわ</t>
+          <t xml:space="preserve">勝利の味は…格別ね</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.normal[2]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[2]</t>
+          <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9971,14 +9971,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うちの団体の底力、見せてあげたわよ</t>
+          <t xml:space="preserve">あら、もう終わり？ 物足りなかったわ</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.normal[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.normal[2]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[3]</t>
+          <t xml:space="preserve">seductive.normal[2]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10003,14 +10003,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、うちの団体の魅力、わかっていただけたかしら</t>
+          <t xml:space="preserve">うちの団体の底力、見せてあげたわよ</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.seductive.normal[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.normal[3]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10020,29 +10020,29 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.seductive.normal[1]</t>
+          <t xml:space="preserve">seductive.normal[3]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来れたのね…最高の気分だわ</t>
+          <t xml:space="preserve">ふふ、うちの団体の魅力、わかっていただけたかしら</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.seductive.normal[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.seductive.normal[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10052,59 +10052,91 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.normal[1]</t>
+          <t xml:space="preserve">fighter.seductive.normal[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わざわざ口説きに来るなんて。…物好きね、あなた。</t>
+          <t xml:space="preserve">ここまで来れたのね…最高の気分だわ</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">FA_GREETING_LINES.seductive.normal[1]</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.normal[1]</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わざわざ口説きに来るなんて。…物好きね、あなた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="40" customHeight="1">
+      <c r="A307" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.seductive.normal[1]</t>
         </is>
       </c>
-      <c r="B306" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr" s="2">
+      <c r="B307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr" s="12">
+      <c r="D307" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">seductive.normal[1]</t>
         </is>
       </c>
-      <c r="E306" t="inlineStr" s="2">
+      <c r="E307" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F306" t="inlineStr" s="3">
+      <c r="F307" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">目をつけたのはそっち。…責任、取ってね</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H306"/>
+  <autoFilter ref="A1:H307"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/蠱惑×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×ノーマル.xlsx
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、正直に言うわ。対戦したい相手が居るのよね。</t>
+          <t xml:space="preserve">社長、正直に言うわ。三人で乗り込みたい所があるのよね。</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="F74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{org}のあの子が気に障るのよね……対戦、セッティングしてくれる？</t>
+          <t xml:space="preserve">あの団体の子が気に障るのよね……三人で乗り込ませてくれる？</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="F75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">理由は言いたくないのだけれど。試合を組んで欲しいの。</t>
+          <t xml:space="preserve">理由は言いたくないのだけれど。三人での遠征、組んで欲しいの。</t>
         </is>
       </c>
     </row>
